--- a/files/NRLW_upcoming_projections.xlsx
+++ b/files/NRLW_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -44,34 +44,52 @@
     <t xml:space="preserve">Weather Applied</t>
   </si>
   <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain (Primary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No - primary model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted (Reference)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference only - heuristic -0.3 total pts/mm, cap +/-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wests tigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george illawarra dragons</t>
+  </si>
+  <si>
     <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commbank stadium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain (Primary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No - primary model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted (Reference)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference only - heuristic -0.3 total pts/mm, cap +/-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fmg stadium waikato</t>
   </si>
 </sst>
 </file>
@@ -410,9 +428,9 @@
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="4.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="15.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="29.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="19.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="29.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="17.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="5.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="28.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="16.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
@@ -454,7 +472,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46208</v>
+        <v>46212</v>
       </c>
       <c r="B2"/>
       <c r="C2" t="s">
@@ -463,28 +481,26 @@
       <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2"/>
+      <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>19.1534851448814</v>
+      </c>
+      <c r="I2" t="n">
+        <v>39.9813771431375</v>
+      </c>
+      <c r="J2" t="s">
         <v>13</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-6.06868760171146</v>
-      </c>
-      <c r="I2" t="n">
-        <v>38.4650393175249</v>
-      </c>
-      <c r="J2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46208</v>
+        <v>46212</v>
       </c>
       <c r="B3"/>
       <c r="C3" t="s">
@@ -493,83 +509,301 @@
       <c r="D3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
+      <c r="E3"/>
       <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>19.1534851448814</v>
+      </c>
+      <c r="I3" t="n">
+        <v>39.9813771431375</v>
+      </c>
+      <c r="J3" t="s">
         <v>15</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-6.06868760171146</v>
-      </c>
-      <c r="I3" t="n">
-        <v>38.3750393175249</v>
-      </c>
-      <c r="J3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B4"/>
       <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
         <v>17</v>
       </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
+      <c r="E4"/>
       <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0213661735589559</v>
+      </c>
+      <c r="I4" t="n">
+        <v>39.2333333333333</v>
+      </c>
+      <c r="J4" t="s">
         <v>13</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.400685686389062</v>
-      </c>
-      <c r="I4" t="n">
-        <v>39.2392344497608</v>
-      </c>
-      <c r="J4" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B5"/>
       <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
         <v>17</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5"/>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.0213661735589559</v>
+      </c>
+      <c r="I5" t="n">
+        <v>39.2333333333333</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B6"/>
+      <c r="C6" t="s">
         <v>18</v>
       </c>
-      <c r="E5" t="s">
+      <c r="D6" t="s">
         <v>19</v>
       </c>
-      <c r="F5" t="s">
+      <c r="E6"/>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-6.6959330531643</v>
+      </c>
+      <c r="I6" t="n">
+        <v>35.3259592494485</v>
+      </c>
+      <c r="J6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B7"/>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7"/>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-6.6959330531643</v>
+      </c>
+      <c r="I7" t="n">
+        <v>35.3259592494485</v>
+      </c>
+      <c r="J7" t="s">
         <v>15</v>
       </c>
-      <c r="G5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.400685686389062</v>
-      </c>
-      <c r="I5" t="n">
-        <v>38.3392344497608</v>
-      </c>
-      <c r="J5" t="s">
-        <v>16</v>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B8"/>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8"/>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-7.37308900963752</v>
+      </c>
+      <c r="I8" t="n">
+        <v>44.9057402072379</v>
+      </c>
+      <c r="J8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B9"/>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9"/>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-7.37308900963752</v>
+      </c>
+      <c r="I9" t="n">
+        <v>44.9057402072379</v>
+      </c>
+      <c r="J9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B10"/>
+      <c r="C10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10"/>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8.11056950023961</v>
+      </c>
+      <c r="I10" t="n">
+        <v>39.9429973412096</v>
+      </c>
+      <c r="J10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B11"/>
+      <c r="C11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11"/>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>8.11056950023961</v>
+      </c>
+      <c r="I11" t="n">
+        <v>39.9429973412096</v>
+      </c>
+      <c r="J11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B12"/>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12"/>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.56109503966957</v>
+      </c>
+      <c r="I12" t="n">
+        <v>40.4190254449825</v>
+      </c>
+      <c r="J12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B13"/>
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13"/>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.56109503966957</v>
+      </c>
+      <c r="I13" t="n">
+        <v>40.4190254449825</v>
+      </c>
+      <c r="J13" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRLW_upcoming_projections.xlsx
+++ b/files/NRLW_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -50,6 +50,9 @@
     <t xml:space="preserve">brisbane broncos</t>
   </si>
   <si>
+    <t xml:space="preserve">ocean protect stadium</t>
+  </si>
+  <si>
     <t xml:space="preserve">No Rain (Primary)</t>
   </si>
   <si>
@@ -68,28 +71,43 @@
     <t xml:space="preserve">gold coast titans</t>
   </si>
   <si>
+    <t xml:space="preserve">accor stadium</t>
+  </si>
+  <si>
     <t xml:space="preserve">north queensland cowboys</t>
   </si>
   <si>
     <t xml:space="preserve">wests tigers</t>
   </si>
   <si>
+    <t xml:space="preserve">queensland country bank stadium</t>
+  </si>
+  <si>
     <t xml:space="preserve">sydney roosters</t>
   </si>
   <si>
     <t xml:space="preserve">newcastle knights</t>
   </si>
   <si>
+    <t xml:space="preserve">allianz stadium</t>
+  </si>
+  <si>
     <t xml:space="preserve">canberra raiders</t>
   </si>
   <si>
     <t xml:space="preserve">warriors</t>
   </si>
   <si>
+    <t xml:space="preserve">gio stadium</t>
+  </si>
+  <si>
     <t xml:space="preserve">st george illawarra dragons</t>
   </si>
   <si>
     <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">win stadium</t>
   </si>
 </sst>
 </file>
@@ -430,7 +448,7 @@
     <col min="2" max="2" width="4.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="29.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="17.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="5.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="31.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="28.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="16.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
@@ -481,12 +499,14 @@
       <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="E2"/>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="H2" t="n">
         <v>19.1534851448814</v>
@@ -495,7 +515,7 @@
         <v>39.9813771431375</v>
       </c>
       <c r="J2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -509,21 +529,23 @@
       <c r="D3" t="s">
         <v>11</v>
       </c>
-      <c r="E3"/>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="H3" t="n">
         <v>19.1534851448814</v>
       </c>
       <c r="I3" t="n">
-        <v>39.9813771431375</v>
+        <v>37.9413771431375</v>
       </c>
       <c r="J3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -532,14 +554,16 @@
       </c>
       <c r="B4"/>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4"/>
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -551,7 +575,7 @@
         <v>39.2333333333333</v>
       </c>
       <c r="J4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -560,14 +584,16 @@
       </c>
       <c r="B5"/>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5"/>
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -579,7 +605,7 @@
         <v>39.2333333333333</v>
       </c>
       <c r="J5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -588,14 +614,16 @@
       </c>
       <c r="B6"/>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6"/>
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
+        <v>22</v>
+      </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -607,7 +635,7 @@
         <v>35.3259592494485</v>
       </c>
       <c r="J6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -616,14 +644,16 @@
       </c>
       <c r="B7"/>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7"/>
+        <v>21</v>
+      </c>
+      <c r="E7" t="s">
+        <v>22</v>
+      </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -635,7 +665,7 @@
         <v>35.3259592494485</v>
       </c>
       <c r="J7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -644,14 +674,16 @@
       </c>
       <c r="B8"/>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8"/>
+        <v>24</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -663,7 +695,7 @@
         <v>44.9057402072379</v>
       </c>
       <c r="J8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -672,14 +704,16 @@
       </c>
       <c r="B9"/>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9"/>
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
+        <v>25</v>
+      </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -691,7 +725,7 @@
         <v>44.9057402072379</v>
       </c>
       <c r="J9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -700,17 +734,19 @@
       </c>
       <c r="B10"/>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10"/>
+        <v>27</v>
+      </c>
+      <c r="E10" t="s">
+        <v>28</v>
+      </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="H10" t="n">
         <v>8.11056950023961</v>
@@ -719,7 +755,7 @@
         <v>39.9429973412096</v>
       </c>
       <c r="J10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -728,26 +764,28 @@
       </c>
       <c r="B11"/>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11"/>
+        <v>27</v>
+      </c>
+      <c r="E11" t="s">
+        <v>28</v>
+      </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="H11" t="n">
         <v>8.11056950023961</v>
       </c>
       <c r="I11" t="n">
-        <v>39.9429973412096</v>
+        <v>38.1729973412096</v>
       </c>
       <c r="J11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -756,14 +794,16 @@
       </c>
       <c r="B12"/>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12"/>
+        <v>30</v>
+      </c>
+      <c r="E12" t="s">
+        <v>31</v>
+      </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -775,7 +815,7 @@
         <v>40.4190254449825</v>
       </c>
       <c r="J12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -784,14 +824,16 @@
       </c>
       <c r="B13"/>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13"/>
+        <v>30</v>
+      </c>
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -803,7 +845,7 @@
         <v>40.4190254449825</v>
       </c>
       <c r="J13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRLW_upcoming_projections.xlsx
+++ b/files/NRLW_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">Weather Applied</t>
   </si>
   <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ocean protect stadium</t>
+    <t xml:space="preserve">canterbury bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accor stadium</t>
   </si>
   <si>
     <t xml:space="preserve">No Rain (Primary)</t>
@@ -63,15 +63,6 @@
   </si>
   <si>
     <t xml:space="preserve">Reference only - heuristic -0.3 total pts/mm, cap +/-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">accor stadium</t>
   </si>
   <si>
     <t xml:space="preserve">north queensland cowboys</t>
@@ -490,7 +481,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46212</v>
+        <v>46214</v>
       </c>
       <c r="B2"/>
       <c r="C2" t="s">
@@ -506,13 +497,13 @@
         <v>13</v>
       </c>
       <c r="G2" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>19.1534851448814</v>
+        <v>0.643539734534159</v>
       </c>
       <c r="I2" t="n">
-        <v>39.9813771431375</v>
+        <v>39.2697674418605</v>
       </c>
       <c r="J2" t="s">
         <v>14</v>
@@ -520,7 +511,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46212</v>
+        <v>46214</v>
       </c>
       <c r="B3"/>
       <c r="C3" t="s">
@@ -536,13 +527,13 @@
         <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>19.1534851448814</v>
+        <v>0.643539734534159</v>
       </c>
       <c r="I3" t="n">
-        <v>37.9413771431375</v>
+        <v>39.2697674418605</v>
       </c>
       <c r="J3" t="s">
         <v>16</v>
@@ -566,13 +557,13 @@
         <v>13</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0213661735589559</v>
+        <v>-4.0919523812184</v>
       </c>
       <c r="I4" t="n">
-        <v>39.2333333333333</v>
+        <v>37.5696515092337</v>
       </c>
       <c r="J4" t="s">
         <v>14</v>
@@ -596,13 +587,13 @@
         <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0213661735589559</v>
+        <v>-4.0919523812184</v>
       </c>
       <c r="I5" t="n">
-        <v>39.2333333333333</v>
+        <v>37.4796515092337</v>
       </c>
       <c r="J5" t="s">
         <v>16</v>
@@ -629,10 +620,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-6.6959330531643</v>
+        <v>-6.93914962442005</v>
       </c>
       <c r="I6" t="n">
-        <v>35.3259592494485</v>
+        <v>41.2678919464872</v>
       </c>
       <c r="J6" t="s">
         <v>14</v>
@@ -659,10 +650,10 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>-6.6959330531643</v>
+        <v>-6.93914962442005</v>
       </c>
       <c r="I7" t="n">
-        <v>35.3259592494485</v>
+        <v>41.2678919464872</v>
       </c>
       <c r="J7" t="s">
         <v>16</v>
@@ -670,7 +661,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B8"/>
       <c r="C8" t="s">
@@ -686,13 +677,13 @@
         <v>13</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="H8" t="n">
-        <v>-7.37308900963752</v>
+        <v>1.31285225907677</v>
       </c>
       <c r="I8" t="n">
-        <v>44.9057402072379</v>
+        <v>43.5098321082488</v>
       </c>
       <c r="J8" t="s">
         <v>14</v>
@@ -700,7 +691,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B9"/>
       <c r="C9" t="s">
@@ -716,13 +707,13 @@
         <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="H9" t="n">
-        <v>-7.37308900963752</v>
+        <v>1.31285225907677</v>
       </c>
       <c r="I9" t="n">
-        <v>44.9057402072379</v>
+        <v>41.8298321082488</v>
       </c>
       <c r="J9" t="s">
         <v>16</v>
@@ -746,13 +737,13 @@
         <v>13</v>
       </c>
       <c r="G10" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>8.11056950023961</v>
+        <v>0.653061731611337</v>
       </c>
       <c r="I10" t="n">
-        <v>39.9429973412096</v>
+        <v>38.3222898254997</v>
       </c>
       <c r="J10" t="s">
         <v>14</v>
@@ -776,75 +767,15 @@
         <v>15</v>
       </c>
       <c r="G11" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>8.11056950023961</v>
+        <v>0.653061731611337</v>
       </c>
       <c r="I11" t="n">
-        <v>38.1729973412096</v>
+        <v>38.3222898254997</v>
       </c>
       <c r="J11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>46215</v>
-      </c>
-      <c r="B12"/>
-      <c r="C12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>3.56109503966957</v>
-      </c>
-      <c r="I12" t="n">
-        <v>40.4190254449825</v>
-      </c>
-      <c r="J12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>46215</v>
-      </c>
-      <c r="B13"/>
-      <c r="C13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>3.56109503966957</v>
-      </c>
-      <c r="I13" t="n">
-        <v>40.4190254449825</v>
-      </c>
-      <c r="J13" t="s">
         <v>16</v>
       </c>
     </row>

--- a/files/NRLW_upcoming_projections.xlsx
+++ b/files/NRLW_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -44,61 +44,70 @@
     <t xml:space="preserve">Weather Applied</t>
   </si>
   <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gio stadium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain (Primary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No - primary model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted (Reference)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference only - heuristic -0.3 total pts/mm, cap +/-6</t>
+  </si>
+  <si>
     <t xml:space="preserve">canterbury bankstown bulldogs</t>
   </si>
   <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accor stadium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">go media stadium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wests tigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">totally workwear stadium</t>
+  </si>
+  <si>
     <t xml:space="preserve">gold coast titans</t>
   </si>
   <si>
-    <t xml:space="preserve">accor stadium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain (Primary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No - primary model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted (Reference)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference only - heuristic -0.3 total pts/mm, cap +/-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">queensland country bank stadium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cbus super stadium</t>
   </si>
   <si>
     <t xml:space="preserve">newcastle knights</t>
   </si>
   <si>
-    <t xml:space="preserve">allianz stadium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gio stadium</t>
-  </si>
-  <si>
     <t xml:space="preserve">st george illawarra dragons</t>
   </si>
   <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">win stadium</t>
+    <t xml:space="preserve">mcdonald jones stadium</t>
   </si>
 </sst>
 </file>
@@ -438,8 +447,8 @@
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="4.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="29.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="17.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="31.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="27.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="24.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="28.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="16.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
@@ -481,7 +490,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B2"/>
       <c r="C2" t="s">
@@ -500,10 +509,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.643539734534159</v>
+        <v>20.4139838300442</v>
       </c>
       <c r="I2" t="n">
-        <v>39.2697674418605</v>
+        <v>46.4039632546516</v>
       </c>
       <c r="J2" t="s">
         <v>14</v>
@@ -511,7 +520,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B3"/>
       <c r="C3" t="s">
@@ -530,10 +539,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.643539734534159</v>
+        <v>20.4139838300442</v>
       </c>
       <c r="I3" t="n">
-        <v>39.2697674418605</v>
+        <v>46.4039632546516</v>
       </c>
       <c r="J3" t="s">
         <v>16</v>
@@ -541,7 +550,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B4"/>
       <c r="C4" t="s">
@@ -557,13 +566,13 @@
         <v>13</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-4.0919523812184</v>
+        <v>5.16988780313592</v>
       </c>
       <c r="I4" t="n">
-        <v>37.5696515092337</v>
+        <v>39.2697674418605</v>
       </c>
       <c r="J4" t="s">
         <v>14</v>
@@ -571,7 +580,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B5"/>
       <c r="C5" t="s">
@@ -587,13 +596,13 @@
         <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.0919523812184</v>
+        <v>5.16988780313592</v>
       </c>
       <c r="I5" t="n">
-        <v>37.4796515092337</v>
+        <v>39.2697674418605</v>
       </c>
       <c r="J5" t="s">
         <v>16</v>
@@ -601,7 +610,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B6"/>
       <c r="C6" t="s">
@@ -620,10 +629,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-6.93914962442005</v>
+        <v>-2.3474257695568</v>
       </c>
       <c r="I6" t="n">
-        <v>41.2678919464872</v>
+        <v>38.1359857396028</v>
       </c>
       <c r="J6" t="s">
         <v>14</v>
@@ -631,7 +640,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B7"/>
       <c r="C7" t="s">
@@ -650,10 +659,10 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>-6.93914962442005</v>
+        <v>-2.3474257695568</v>
       </c>
       <c r="I7" t="n">
-        <v>41.2678919464872</v>
+        <v>38.1359857396028</v>
       </c>
       <c r="J7" t="s">
         <v>16</v>
@@ -661,7 +670,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B8"/>
       <c r="C8" t="s">
@@ -677,13 +686,13 @@
         <v>13</v>
       </c>
       <c r="G8" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1.31285225907677</v>
+        <v>-31.1515608808005</v>
       </c>
       <c r="I8" t="n">
-        <v>43.5098321082488</v>
+        <v>43.8584480636318</v>
       </c>
       <c r="J8" t="s">
         <v>14</v>
@@ -691,7 +700,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B9"/>
       <c r="C9" t="s">
@@ -707,13 +716,13 @@
         <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1.31285225907677</v>
+        <v>-31.1515608808005</v>
       </c>
       <c r="I9" t="n">
-        <v>41.8298321082488</v>
+        <v>43.8584480636318</v>
       </c>
       <c r="J9" t="s">
         <v>16</v>
@@ -721,7 +730,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B10"/>
       <c r="C10" t="s">
@@ -740,10 +749,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.653061731611337</v>
+        <v>-3.96947877753608</v>
       </c>
       <c r="I10" t="n">
-        <v>38.3222898254997</v>
+        <v>36.6635543626358</v>
       </c>
       <c r="J10" t="s">
         <v>14</v>
@@ -751,7 +760,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B11"/>
       <c r="C11" t="s">
@@ -770,12 +779,72 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.653061731611337</v>
+        <v>-3.96947877753608</v>
       </c>
       <c r="I11" t="n">
-        <v>38.3222898254997</v>
+        <v>36.6635543626358</v>
       </c>
       <c r="J11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B12"/>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-12.645815833934</v>
+      </c>
+      <c r="I12" t="n">
+        <v>37.5095732369552</v>
+      </c>
+      <c r="J12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B13"/>
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-12.645815833934</v>
+      </c>
+      <c r="I13" t="n">
+        <v>37.5095732369552</v>
+      </c>
+      <c r="J13" t="s">
         <v>16</v>
       </c>
     </row>

--- a/files/NRLW_upcoming_projections.xlsx
+++ b/files/NRLW_upcoming_projections.xlsx
@@ -44,70 +44,70 @@
     <t xml:space="preserve">Weather Applied</t>
   </si>
   <si>
+    <t xml:space="preserve">12:45</t>
+  </si>
+  <si>
     <t xml:space="preserve">canberra raiders</t>
   </si>
   <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain (Primary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No - primary model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted (Reference)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference only - heuristic -0.3 total pts/mm, cap +/-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wests tigers</t>
+  </si>
+  <si>
     <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gio stadium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain (Primary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No - primary model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted (Reference)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference only - heuristic -0.3 total pts/mm, cap +/-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">accor stadium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">go media stadium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">totally workwear stadium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cbus super stadium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mcdonald jones stadium</t>
   </si>
 </sst>
 </file>
@@ -445,10 +445,10 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="4.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="5.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="29.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="27.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="24.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="5.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="28.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="16.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
@@ -490,18 +490,18 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46221</v>
-      </c>
-      <c r="B2"/>
+        <v>46228</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
         <v>12</v>
       </c>
+      <c r="E2"/>
       <c r="F2" t="s">
         <v>13</v>
       </c>
@@ -509,10 +509,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>20.4139838300442</v>
+        <v>-0.303507102607753</v>
       </c>
       <c r="I2" t="n">
-        <v>46.4039632546516</v>
+        <v>41.6289886221357</v>
       </c>
       <c r="J2" t="s">
         <v>14</v>
@@ -520,18 +520,18 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46221</v>
-      </c>
-      <c r="B3"/>
+        <v>46228</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
         <v>12</v>
       </c>
+      <c r="E3"/>
       <c r="F3" t="s">
         <v>15</v>
       </c>
@@ -539,10 +539,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>20.4139838300442</v>
+        <v>-0.303507102607753</v>
       </c>
       <c r="I3" t="n">
-        <v>46.4039632546516</v>
+        <v>41.6289886221357</v>
       </c>
       <c r="J3" t="s">
         <v>16</v>
@@ -550,18 +550,18 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46221</v>
-      </c>
-      <c r="B4"/>
+        <v>46228</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
         <v>19</v>
       </c>
+      <c r="E4"/>
       <c r="F4" t="s">
         <v>13</v>
       </c>
@@ -569,10 +569,10 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>5.16988780313592</v>
+        <v>0.983632499907437</v>
       </c>
       <c r="I4" t="n">
-        <v>39.2697674418605</v>
+        <v>41.7712962852712</v>
       </c>
       <c r="J4" t="s">
         <v>14</v>
@@ -580,18 +580,18 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46221</v>
-      </c>
-      <c r="B5"/>
+        <v>46228</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
         <v>19</v>
       </c>
+      <c r="E5"/>
       <c r="F5" t="s">
         <v>15</v>
       </c>
@@ -599,10 +599,10 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5.16988780313592</v>
+        <v>0.983632499907437</v>
       </c>
       <c r="I5" t="n">
-        <v>39.2697674418605</v>
+        <v>41.7712962852712</v>
       </c>
       <c r="J5" t="s">
         <v>16</v>
@@ -610,18 +610,18 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46221</v>
-      </c>
-      <c r="B6"/>
+        <v>46228</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" t="s">
         <v>22</v>
       </c>
+      <c r="E6"/>
       <c r="F6" t="s">
         <v>13</v>
       </c>
@@ -629,10 +629,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.3474257695568</v>
+        <v>7.75404316407071</v>
       </c>
       <c r="I6" t="n">
-        <v>38.1359857396028</v>
+        <v>42.276371231609</v>
       </c>
       <c r="J6" t="s">
         <v>14</v>
@@ -640,18 +640,18 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46221</v>
-      </c>
-      <c r="B7"/>
+        <v>46228</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" t="s">
         <v>22</v>
       </c>
+      <c r="E7"/>
       <c r="F7" t="s">
         <v>15</v>
       </c>
@@ -659,10 +659,10 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.3474257695568</v>
+        <v>7.75404316407071</v>
       </c>
       <c r="I7" t="n">
-        <v>38.1359857396028</v>
+        <v>42.276371231609</v>
       </c>
       <c r="J7" t="s">
         <v>16</v>
@@ -670,18 +670,18 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="B8"/>
+        <v>46229</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" t="s">
         <v>25</v>
       </c>
+      <c r="E8"/>
       <c r="F8" t="s">
         <v>13</v>
       </c>
@@ -689,10 +689,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>-31.1515608808005</v>
+        <v>-7.41245114487048</v>
       </c>
       <c r="I8" t="n">
-        <v>43.8584480636318</v>
+        <v>42.7035756695531</v>
       </c>
       <c r="J8" t="s">
         <v>14</v>
@@ -700,18 +700,18 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="B9"/>
+        <v>46229</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" t="s">
         <v>25</v>
       </c>
+      <c r="E9"/>
       <c r="F9" t="s">
         <v>15</v>
       </c>
@@ -719,10 +719,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>-31.1515608808005</v>
+        <v>-7.41245114487048</v>
       </c>
       <c r="I9" t="n">
-        <v>43.8584480636318</v>
+        <v>42.7035756695531</v>
       </c>
       <c r="J9" t="s">
         <v>16</v>
@@ -730,18 +730,18 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="B10"/>
+        <v>46229</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" t="s">
         <v>28</v>
       </c>
+      <c r="E10"/>
       <c r="F10" t="s">
         <v>13</v>
       </c>
@@ -749,10 +749,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.96947877753608</v>
+        <v>7.06506353550224</v>
       </c>
       <c r="I10" t="n">
-        <v>36.6635543626358</v>
+        <v>43.828153134857</v>
       </c>
       <c r="J10" t="s">
         <v>14</v>
@@ -760,18 +760,18 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="B11"/>
+        <v>46229</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" t="s">
         <v>28</v>
       </c>
+      <c r="E11"/>
       <c r="F11" t="s">
         <v>15</v>
       </c>
@@ -779,10 +779,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.96947877753608</v>
+        <v>7.06506353550224</v>
       </c>
       <c r="I11" t="n">
-        <v>36.6635543626358</v>
+        <v>43.828153134857</v>
       </c>
       <c r="J11" t="s">
         <v>16</v>
@@ -790,18 +790,18 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="B12"/>
+        <v>46229</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" t="s">
         <v>31</v>
       </c>
+      <c r="E12"/>
       <c r="F12" t="s">
         <v>13</v>
       </c>
@@ -809,10 +809,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>-12.645815833934</v>
+        <v>13.6158206827388</v>
       </c>
       <c r="I12" t="n">
-        <v>37.5095732369552</v>
+        <v>42.1231998919844</v>
       </c>
       <c r="J12" t="s">
         <v>14</v>
@@ -820,18 +820,18 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="B13"/>
+        <v>46229</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" t="s">
         <v>31</v>
       </c>
+      <c r="E13"/>
       <c r="F13" t="s">
         <v>15</v>
       </c>
@@ -839,10 +839,10 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>-12.645815833934</v>
+        <v>13.6158206827388</v>
       </c>
       <c r="I13" t="n">
-        <v>37.5095732369552</v>
+        <v>42.1231998919844</v>
       </c>
       <c r="J13" t="s">
         <v>16</v>

--- a/files/NRLW_upcoming_projections.xlsx
+++ b/files/NRLW_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -44,70 +44,76 @@
     <t xml:space="preserve">Weather Applied</t>
   </si>
   <si>
-    <t xml:space="preserve">12:45</t>
+    <t xml:space="preserve">15:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain (Primary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No - primary model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted (Reference)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference only - heuristic -0.3 total pts/mm, cap +/-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wests tigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:15</t>
   </si>
   <si>
     <t xml:space="preserve">canberra raiders</t>
   </si>
   <si>
+    <t xml:space="preserve">12:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">cronulla-sutherland sharks</t>
   </si>
   <si>
-    <t xml:space="preserve">No Rain (Primary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No - primary model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted (Reference)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference only - heuristic -0.3 total pts/mm, cap +/-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
+    <t xml:space="preserve">14:15</t>
   </si>
 </sst>
 </file>
@@ -509,10 +515,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.303507102607753</v>
+        <v>0.983632499907437</v>
       </c>
       <c r="I2" t="n">
-        <v>41.6289886221357</v>
+        <v>41.7712962852712</v>
       </c>
       <c r="J2" t="s">
         <v>14</v>
@@ -539,10 +545,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.303507102607753</v>
+        <v>0.983632499907437</v>
       </c>
       <c r="I3" t="n">
-        <v>41.6289886221357</v>
+        <v>41.7712962852712</v>
       </c>
       <c r="J3" t="s">
         <v>16</v>
@@ -569,10 +575,10 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.983632499907437</v>
+        <v>7.75404316407071</v>
       </c>
       <c r="I4" t="n">
-        <v>41.7712962852712</v>
+        <v>42.276371231609</v>
       </c>
       <c r="J4" t="s">
         <v>14</v>
@@ -599,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.983632499907437</v>
+        <v>7.75404316407071</v>
       </c>
       <c r="I5" t="n">
-        <v>41.7712962852712</v>
+        <v>42.276371231609</v>
       </c>
       <c r="J5" t="s">
         <v>16</v>
@@ -610,7 +616,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
@@ -629,10 +635,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>7.75404316407071</v>
+        <v>-7.41245114487048</v>
       </c>
       <c r="I6" t="n">
-        <v>42.276371231609</v>
+        <v>42.7035756695531</v>
       </c>
       <c r="J6" t="s">
         <v>14</v>
@@ -640,7 +646,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
@@ -659,10 +665,10 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>7.75404316407071</v>
+        <v>-7.41245114487048</v>
       </c>
       <c r="I7" t="n">
-        <v>42.276371231609</v>
+        <v>42.7035756695531</v>
       </c>
       <c r="J7" t="s">
         <v>16</v>
@@ -689,10 +695,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>-7.41245114487048</v>
+        <v>7.06506353550224</v>
       </c>
       <c r="I8" t="n">
-        <v>42.7035756695531</v>
+        <v>43.828153134857</v>
       </c>
       <c r="J8" t="s">
         <v>14</v>
@@ -719,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>-7.41245114487048</v>
+        <v>7.06506353550224</v>
       </c>
       <c r="I9" t="n">
-        <v>42.7035756695531</v>
+        <v>43.828153134857</v>
       </c>
       <c r="J9" t="s">
         <v>16</v>
@@ -749,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>7.06506353550224</v>
+        <v>13.6158206827388</v>
       </c>
       <c r="I10" t="n">
-        <v>43.828153134857</v>
+        <v>42.1231998919844</v>
       </c>
       <c r="J10" t="s">
         <v>14</v>
@@ -779,10 +785,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>7.06506353550224</v>
+        <v>13.6158206827388</v>
       </c>
       <c r="I11" t="n">
-        <v>43.828153134857</v>
+        <v>42.1231998919844</v>
       </c>
       <c r="J11" t="s">
         <v>16</v>
@@ -790,7 +796,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B12" t="s">
         <v>29</v>
@@ -799,7 +805,7 @@
         <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E12"/>
       <c r="F12" t="s">
@@ -809,10 +815,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>13.6158206827388</v>
+        <v>-6.60121107254077</v>
       </c>
       <c r="I12" t="n">
-        <v>42.1231998919844</v>
+        <v>43.8126896797634</v>
       </c>
       <c r="J12" t="s">
         <v>14</v>
@@ -820,7 +826,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B13" t="s">
         <v>29</v>
@@ -829,7 +835,7 @@
         <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E13"/>
       <c r="F13" t="s">
@@ -839,12 +845,132 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>13.6158206827388</v>
+        <v>-6.60121107254077</v>
       </c>
       <c r="I13" t="n">
-        <v>42.1231998919844</v>
+        <v>43.8126896797634</v>
       </c>
       <c r="J13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14"/>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-4.67780731917525</v>
+      </c>
+      <c r="I14" t="n">
+        <v>39.861449808901</v>
+      </c>
+      <c r="J14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15"/>
+      <c r="F15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-4.67780731917525</v>
+      </c>
+      <c r="I15" t="n">
+        <v>39.861449808901</v>
+      </c>
+      <c r="J15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16"/>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>13.7837410781809</v>
+      </c>
+      <c r="I16" t="n">
+        <v>39.7411296607424</v>
+      </c>
+      <c r="J16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17"/>
+      <c r="F17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>13.7837410781809</v>
+      </c>
+      <c r="I17" t="n">
+        <v>39.7411296607424</v>
+      </c>
+      <c r="J17" t="s">
         <v>16</v>
       </c>
     </row>

--- a/files/NRLW_upcoming_projections.xlsx
+++ b/files/NRLW_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -44,76 +44,67 @@
     <t xml:space="preserve">Weather Applied</t>
   </si>
   <si>
-    <t xml:space="preserve">15:15</t>
+    <t xml:space="preserve">16:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain (Primary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No - primary model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted (Reference)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference only - heuristic -0.3 total pts/mm, cap +/-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wests tigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
   </si>
   <si>
     <t xml:space="preserve">canterbury bankstown bulldogs</t>
   </si>
   <si>
-    <t xml:space="preserve">st george illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain (Primary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No - primary model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted (Reference)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference only - heuristic -0.3 total pts/mm, cap +/-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:45</t>
   </si>
   <si>
     <t xml:space="preserve">gold coast titans</t>
   </si>
   <si>
-    <t xml:space="preserve">13:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
   </si>
   <si>
     <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:15</t>
   </si>
 </sst>
 </file>
@@ -453,7 +444,7 @@
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="5.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="29.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="27.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="24.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="5.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="28.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="16.71" hidden="0" customWidth="1"/>
@@ -496,7 +487,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -515,10 +506,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.983632499907437</v>
+        <v>-6.72006514133476</v>
       </c>
       <c r="I2" t="n">
-        <v>41.7712962852712</v>
+        <v>42.366188954353</v>
       </c>
       <c r="J2" t="s">
         <v>14</v>
@@ -526,7 +517,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
@@ -545,10 +536,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.983632499907437</v>
+        <v>-6.72006514133476</v>
       </c>
       <c r="I3" t="n">
-        <v>41.7712962852712</v>
+        <v>42.366188954353</v>
       </c>
       <c r="J3" t="s">
         <v>16</v>
@@ -556,7 +547,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
@@ -575,10 +566,10 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>7.75404316407071</v>
+        <v>-7.2917059609182</v>
       </c>
       <c r="I4" t="n">
-        <v>42.276371231609</v>
+        <v>40.053583250296</v>
       </c>
       <c r="J4" t="s">
         <v>14</v>
@@ -586,7 +577,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B5" t="s">
         <v>17</v>
@@ -605,10 +596,10 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>7.75404316407071</v>
+        <v>-7.2917059609182</v>
       </c>
       <c r="I5" t="n">
-        <v>42.276371231609</v>
+        <v>40.053583250296</v>
       </c>
       <c r="J5" t="s">
         <v>16</v>
@@ -616,7 +607,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
@@ -635,10 +626,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-7.41245114487048</v>
+        <v>17.1491337628528</v>
       </c>
       <c r="I6" t="n">
-        <v>42.7035756695531</v>
+        <v>40.1455735564871</v>
       </c>
       <c r="J6" t="s">
         <v>14</v>
@@ -646,7 +637,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
@@ -665,10 +656,10 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>-7.41245114487048</v>
+        <v>17.1491337628528</v>
       </c>
       <c r="I7" t="n">
-        <v>42.7035756695531</v>
+        <v>40.1455735564871</v>
       </c>
       <c r="J7" t="s">
         <v>16</v>
@@ -676,16 +667,16 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
         <v>23</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>24</v>
-      </c>
-      <c r="D8" t="s">
-        <v>25</v>
       </c>
       <c r="E8"/>
       <c r="F8" t="s">
@@ -695,10 +686,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>7.06506353550224</v>
+        <v>18.1348218421501</v>
       </c>
       <c r="I8" t="n">
-        <v>43.828153134857</v>
+        <v>45.3646506758072</v>
       </c>
       <c r="J8" t="s">
         <v>14</v>
@@ -706,16 +697,16 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
         <v>23</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>24</v>
-      </c>
-      <c r="D9" t="s">
-        <v>25</v>
       </c>
       <c r="E9"/>
       <c r="F9" t="s">
@@ -725,10 +716,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>7.06506353550224</v>
+        <v>18.1348218421501</v>
       </c>
       <c r="I9" t="n">
-        <v>43.828153134857</v>
+        <v>45.3646506758072</v>
       </c>
       <c r="J9" t="s">
         <v>16</v>
@@ -736,16 +727,16 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
         <v>26</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>27</v>
-      </c>
-      <c r="D10" t="s">
-        <v>28</v>
       </c>
       <c r="E10"/>
       <c r="F10" t="s">
@@ -755,10 +746,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>13.6158206827388</v>
+        <v>-0.777875484334724</v>
       </c>
       <c r="I10" t="n">
-        <v>42.1231998919844</v>
+        <v>41.4416848335443</v>
       </c>
       <c r="J10" t="s">
         <v>14</v>
@@ -766,16 +757,16 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
         <v>26</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>27</v>
-      </c>
-      <c r="D11" t="s">
-        <v>28</v>
       </c>
       <c r="E11"/>
       <c r="F11" t="s">
@@ -785,10 +776,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>13.6158206827388</v>
+        <v>-0.777875484334724</v>
       </c>
       <c r="I11" t="n">
-        <v>42.1231998919844</v>
+        <v>41.4416848335443</v>
       </c>
       <c r="J11" t="s">
         <v>16</v>
@@ -796,16 +787,16 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
         <v>29</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>30</v>
-      </c>
-      <c r="D12" t="s">
-        <v>18</v>
       </c>
       <c r="E12"/>
       <c r="F12" t="s">
@@ -815,10 +806,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>-6.60121107254077</v>
+        <v>9.47144604765844</v>
       </c>
       <c r="I12" t="n">
-        <v>43.8126896797634</v>
+        <v>39.7045226067663</v>
       </c>
       <c r="J12" t="s">
         <v>14</v>
@@ -826,16 +817,16 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" t="s">
         <v>29</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>30</v>
-      </c>
-      <c r="D13" t="s">
-        <v>18</v>
       </c>
       <c r="E13"/>
       <c r="F13" t="s">
@@ -845,132 +836,12 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>-6.60121107254077</v>
+        <v>9.47144604765844</v>
       </c>
       <c r="I13" t="n">
-        <v>43.8126896797634</v>
+        <v>39.7045226067663</v>
       </c>
       <c r="J13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>46235</v>
-      </c>
-      <c r="B14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14"/>
-      <c r="F14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-4.67780731917525</v>
-      </c>
-      <c r="I14" t="n">
-        <v>39.861449808901</v>
-      </c>
-      <c r="J14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>46235</v>
-      </c>
-      <c r="B15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15"/>
-      <c r="F15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-4.67780731917525</v>
-      </c>
-      <c r="I15" t="n">
-        <v>39.861449808901</v>
-      </c>
-      <c r="J15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>46235</v>
-      </c>
-      <c r="B16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16"/>
-      <c r="F16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>13.7837410781809</v>
-      </c>
-      <c r="I16" t="n">
-        <v>39.7411296607424</v>
-      </c>
-      <c r="J16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>46235</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17"/>
-      <c r="F17" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>13.7837410781809</v>
-      </c>
-      <c r="I17" t="n">
-        <v>39.7411296607424</v>
-      </c>
-      <c r="J17" t="s">
         <v>16</v>
       </c>
     </row>

--- a/files/NRLW_upcoming_projections.xlsx
+++ b/files/NRLW_upcoming_projections.xlsx
@@ -506,10 +506,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-6.72006514133476</v>
+        <v>-6.700875957589</v>
       </c>
       <c r="I2" t="n">
-        <v>42.366188954353</v>
+        <v>42.4011142834132</v>
       </c>
       <c r="J2" t="s">
         <v>14</v>
@@ -536,10 +536,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-6.72006514133476</v>
+        <v>-6.700875957589</v>
       </c>
       <c r="I3" t="n">
-        <v>42.366188954353</v>
+        <v>42.4011142834132</v>
       </c>
       <c r="J3" t="s">
         <v>16</v>
@@ -566,10 +566,10 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-7.2917059609182</v>
+        <v>-7.65029102380078</v>
       </c>
       <c r="I4" t="n">
-        <v>40.053583250296</v>
+        <v>40.0302824505684</v>
       </c>
       <c r="J4" t="s">
         <v>14</v>
@@ -596,10 +596,10 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-7.2917059609182</v>
+        <v>-7.65029102380078</v>
       </c>
       <c r="I5" t="n">
-        <v>40.053583250296</v>
+        <v>40.0302824505684</v>
       </c>
       <c r="J5" t="s">
         <v>16</v>
@@ -626,10 +626,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>17.1491337628528</v>
+        <v>17.5656481009565</v>
       </c>
       <c r="I6" t="n">
-        <v>40.1455735564871</v>
+        <v>40.1081508156455</v>
       </c>
       <c r="J6" t="s">
         <v>14</v>
@@ -656,10 +656,10 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>17.1491337628528</v>
+        <v>17.5656481009565</v>
       </c>
       <c r="I7" t="n">
-        <v>40.1455735564871</v>
+        <v>40.1081508156455</v>
       </c>
       <c r="J7" t="s">
         <v>16</v>
@@ -686,10 +686,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>18.1348218421501</v>
+        <v>18.2060504530342</v>
       </c>
       <c r="I8" t="n">
-        <v>45.3646506758072</v>
+        <v>45.3799865266716</v>
       </c>
       <c r="J8" t="s">
         <v>14</v>
@@ -716,10 +716,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>18.1348218421501</v>
+        <v>18.2060504530342</v>
       </c>
       <c r="I9" t="n">
-        <v>45.3646506758072</v>
+        <v>45.3799865266716</v>
       </c>
       <c r="J9" t="s">
         <v>16</v>
@@ -746,10 +746,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.777875484334724</v>
+        <v>-0.788392402770229</v>
       </c>
       <c r="I10" t="n">
-        <v>41.4416848335443</v>
+        <v>41.4579676856779</v>
       </c>
       <c r="J10" t="s">
         <v>14</v>
@@ -776,10 +776,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.777875484334724</v>
+        <v>-0.788392402770229</v>
       </c>
       <c r="I11" t="n">
-        <v>41.4416848335443</v>
+        <v>41.4579676856779</v>
       </c>
       <c r="J11" t="s">
         <v>16</v>
@@ -806,10 +806,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>9.47144604765844</v>
+        <v>9.60010798510654</v>
       </c>
       <c r="I12" t="n">
-        <v>39.7045226067663</v>
+        <v>39.7381661260558</v>
       </c>
       <c r="J12" t="s">
         <v>14</v>
@@ -836,10 +836,10 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>9.47144604765844</v>
+        <v>9.60010798510654</v>
       </c>
       <c r="I13" t="n">
-        <v>39.7045226067663</v>
+        <v>39.7381661260558</v>
       </c>
       <c r="J13" t="s">
         <v>16</v>

--- a/files/NRLW_upcoming_projections.xlsx
+++ b/files/NRLW_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -44,67 +44,70 @@
     <t xml:space="preserve">Weather Applied</t>
   </si>
   <si>
-    <t xml:space="preserve">16:15</t>
+    <t xml:space="preserve">12:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain (Primary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No - primary model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted (Reference)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference only - heuristic -0.3 total pts/mm, cap +/-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:50</t>
   </si>
   <si>
     <t xml:space="preserve">canberra raiders</t>
   </si>
   <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain (Primary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No - primary model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted (Reference)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference only - heuristic -0.3 total pts/mm, cap +/-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george illawarra dragons</t>
   </si>
   <si>
     <t xml:space="preserve">wests tigers</t>
   </si>
   <si>
-    <t xml:space="preserve">14:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george illawarra dragons</t>
+    <t xml:space="preserve">18:15</t>
   </si>
   <si>
     <t xml:space="preserve">sydney roosters</t>
   </si>
   <si>
-    <t xml:space="preserve">canterbury bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:00</t>
-  </si>
-  <si>
     <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
   </si>
 </sst>
 </file>
@@ -487,7 +490,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46235</v>
+        <v>46242</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -506,10 +509,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-6.700875957589</v>
+        <v>-0.967365923161965</v>
       </c>
       <c r="I2" t="n">
-        <v>42.4011142834132</v>
+        <v>41.1347508280856</v>
       </c>
       <c r="J2" t="s">
         <v>14</v>
@@ -517,7 +520,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46235</v>
+        <v>46242</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
@@ -536,10 +539,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-6.700875957589</v>
+        <v>-0.967365923161965</v>
       </c>
       <c r="I3" t="n">
-        <v>42.4011142834132</v>
+        <v>41.1347508280856</v>
       </c>
       <c r="J3" t="s">
         <v>16</v>
@@ -547,7 +550,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46235</v>
+        <v>46242</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
@@ -566,10 +569,10 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-7.65029102380078</v>
+        <v>2.95591997136961</v>
       </c>
       <c r="I4" t="n">
-        <v>40.0302824505684</v>
+        <v>39.0546153809696</v>
       </c>
       <c r="J4" t="s">
         <v>14</v>
@@ -577,7 +580,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46235</v>
+        <v>46242</v>
       </c>
       <c r="B5" t="s">
         <v>17</v>
@@ -596,10 +599,10 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-7.65029102380078</v>
+        <v>2.95591997136961</v>
       </c>
       <c r="I5" t="n">
-        <v>40.0302824505684</v>
+        <v>39.0546153809696</v>
       </c>
       <c r="J5" t="s">
         <v>16</v>
@@ -607,7 +610,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46235</v>
+        <v>46242</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
@@ -626,10 +629,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>17.5656481009565</v>
+        <v>4.30523197794122</v>
       </c>
       <c r="I6" t="n">
-        <v>40.1081508156455</v>
+        <v>39.4395417954011</v>
       </c>
       <c r="J6" t="s">
         <v>14</v>
@@ -637,7 +640,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46235</v>
+        <v>46242</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
@@ -656,10 +659,10 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>17.5656481009565</v>
+        <v>4.30523197794122</v>
       </c>
       <c r="I7" t="n">
-        <v>40.1081508156455</v>
+        <v>39.4395417954011</v>
       </c>
       <c r="J7" t="s">
         <v>16</v>
@@ -667,16 +670,16 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46236</v>
+        <v>46243</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E8"/>
       <c r="F8" t="s">
@@ -686,10 +689,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>18.2060504530342</v>
+        <v>16.5034438582445</v>
       </c>
       <c r="I8" t="n">
-        <v>45.3799865266716</v>
+        <v>44.3103951350002</v>
       </c>
       <c r="J8" t="s">
         <v>14</v>
@@ -697,16 +700,16 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46236</v>
+        <v>46243</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9"/>
       <c r="F9" t="s">
@@ -716,10 +719,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>18.2060504530342</v>
+        <v>16.5034438582445</v>
       </c>
       <c r="I9" t="n">
-        <v>45.3799865266716</v>
+        <v>44.3103951350002</v>
       </c>
       <c r="J9" t="s">
         <v>16</v>
@@ -727,16 +730,16 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46236</v>
+        <v>46243</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E10"/>
       <c r="F10" t="s">
@@ -746,10 +749,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.788392402770229</v>
+        <v>1.91884346032829</v>
       </c>
       <c r="I10" t="n">
-        <v>41.4579676856779</v>
+        <v>41.93872955763</v>
       </c>
       <c r="J10" t="s">
         <v>14</v>
@@ -757,16 +760,16 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46236</v>
+        <v>46243</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E11"/>
       <c r="F11" t="s">
@@ -776,10 +779,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.788392402770229</v>
+        <v>1.91884346032829</v>
       </c>
       <c r="I11" t="n">
-        <v>41.4579676856779</v>
+        <v>41.93872955763</v>
       </c>
       <c r="J11" t="s">
         <v>16</v>
@@ -787,16 +790,16 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46236</v>
+        <v>46243</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E12"/>
       <c r="F12" t="s">
@@ -806,10 +809,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>9.60010798510654</v>
+        <v>-17.4666918131983</v>
       </c>
       <c r="I12" t="n">
-        <v>39.7381661260558</v>
+        <v>43.0792761429269</v>
       </c>
       <c r="J12" t="s">
         <v>14</v>
@@ -817,16 +820,16 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46236</v>
+        <v>46243</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E13"/>
       <c r="F13" t="s">
@@ -836,10 +839,10 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>9.60010798510654</v>
+        <v>-17.4666918131983</v>
       </c>
       <c r="I13" t="n">
-        <v>39.7381661260558</v>
+        <v>43.0792761429269</v>
       </c>
       <c r="J13" t="s">
         <v>16</v>

--- a/files/NRLW_upcoming_projections.xlsx
+++ b/files/NRLW_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -26,21 +26,24 @@
     <t xml:space="preserve">Away Team</t>
   </si>
   <si>
+    <t xml:space="preserve">Selected / Hybrid Home Line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM Home Line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLAYER Home Line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projected Total</t>
+  </si>
+  <si>
     <t xml:space="preserve">Venue</t>
   </si>
   <si>
-    <t xml:space="preserve">Projection Type</t>
-  </si>
-  <si>
     <t xml:space="preserve">Forecast Rain mm</t>
   </si>
   <si>
-    <t xml:space="preserve">Home Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total</t>
-  </si>
-  <si>
     <t xml:space="preserve">Weather Applied</t>
   </si>
   <si>
@@ -53,13 +56,7 @@
     <t xml:space="preserve">north queensland cowboys</t>
   </si>
   <si>
-    <t xml:space="preserve">No Rain (Primary)</t>
-  </si>
-  <si>
     <t xml:space="preserve">No - primary model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted (Reference)</t>
   </si>
   <si>
     <t xml:space="preserve">Reference only - heuristic -0.3 total pts/mm, cap +/-6</t>
@@ -448,12 +445,13 @@
     <col min="2" max="2" width="5.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="29.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="24.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="5.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="28.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="27.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="16.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="11.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="54.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="15.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="5.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="16.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="54.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -487,34 +485,40 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
         <v>46242</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2"/>
-      <c r="F2" t="s">
         <v>13</v>
       </c>
+      <c r="E2" t="n">
+        <v>-0.967365923161965</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.967365923161965</v>
+      </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.885127034852399</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.967365923161965</v>
-      </c>
-      <c r="I2" t="n">
         <v>41.1347508280856</v>
       </c>
-      <c r="J2" t="s">
+      <c r="I2"/>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -523,29 +527,32 @@
         <v>46242</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3"/>
-      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.967365923161965</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.967365923161965</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.885127034852399</v>
+      </c>
+      <c r="H3" t="n">
+        <v>41.1347508280856</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="s">
         <v>15</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-0.967365923161965</v>
-      </c>
-      <c r="I3" t="n">
-        <v>41.1347508280856</v>
-      </c>
-      <c r="J3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -553,28 +560,31 @@
         <v>46242</v>
       </c>
       <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>18</v>
       </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4"/>
-      <c r="F4" t="s">
-        <v>13</v>
+      <c r="E4" t="n">
+        <v>2.95591997136961</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.95591997136961</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>6.83914463048428</v>
       </c>
       <c r="H4" t="n">
-        <v>2.95591997136961</v>
-      </c>
-      <c r="I4" t="n">
         <v>39.0546153809696</v>
       </c>
-      <c r="J4" t="s">
+      <c r="I4"/>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -583,29 +593,32 @@
         <v>46242</v>
       </c>
       <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>18</v>
       </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5"/>
-      <c r="F5" t="s">
+      <c r="E5" t="n">
+        <v>2.95591997136961</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.95591997136961</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6.83914463048428</v>
+      </c>
+      <c r="H5" t="n">
+        <v>39.0546153809696</v>
+      </c>
+      <c r="I5"/>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
         <v>15</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.95591997136961</v>
-      </c>
-      <c r="I5" t="n">
-        <v>39.0546153809696</v>
-      </c>
-      <c r="J5" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -613,28 +626,31 @@
         <v>46242</v>
       </c>
       <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
         <v>20</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>21</v>
       </c>
-      <c r="D6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6"/>
-      <c r="F6" t="s">
-        <v>13</v>
+      <c r="E6" t="n">
+        <v>4.30523197794122</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4.30523197794122</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.754367052351461</v>
       </c>
       <c r="H6" t="n">
-        <v>4.30523197794122</v>
-      </c>
-      <c r="I6" t="n">
         <v>39.4395417954011</v>
       </c>
-      <c r="J6" t="s">
+      <c r="I6"/>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -643,29 +659,32 @@
         <v>46242</v>
       </c>
       <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
         <v>20</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>21</v>
       </c>
-      <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7"/>
-      <c r="F7" t="s">
+      <c r="E7" t="n">
+        <v>4.30523197794122</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4.30523197794122</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.754367052351461</v>
+      </c>
+      <c r="H7" t="n">
+        <v>39.4395417954011</v>
+      </c>
+      <c r="I7"/>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="s">
         <v>15</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4.30523197794122</v>
-      </c>
-      <c r="I7" t="n">
-        <v>39.4395417954011</v>
-      </c>
-      <c r="J7" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -673,28 +692,31 @@
         <v>46243</v>
       </c>
       <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
         <v>23</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>24</v>
       </c>
-      <c r="D8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8"/>
-      <c r="F8" t="s">
-        <v>13</v>
+      <c r="E8" t="n">
+        <v>16.5034438582445</v>
+      </c>
+      <c r="F8" t="n">
+        <v>16.5034438582445</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>10.2754320846569</v>
       </c>
       <c r="H8" t="n">
-        <v>16.5034438582445</v>
-      </c>
-      <c r="I8" t="n">
         <v>44.3103951350002</v>
       </c>
-      <c r="J8" t="s">
+      <c r="I8"/>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="s">
         <v>14</v>
       </c>
     </row>
@@ -703,29 +725,32 @@
         <v>46243</v>
       </c>
       <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
         <v>23</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>24</v>
       </c>
-      <c r="D9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9"/>
-      <c r="F9" t="s">
+      <c r="E9" t="n">
+        <v>16.5034438582445</v>
+      </c>
+      <c r="F9" t="n">
+        <v>16.5034438582445</v>
+      </c>
+      <c r="G9" t="n">
+        <v>10.2754320846569</v>
+      </c>
+      <c r="H9" t="n">
+        <v>44.3103951350002</v>
+      </c>
+      <c r="I9"/>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="s">
         <v>15</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>16.5034438582445</v>
-      </c>
-      <c r="I9" t="n">
-        <v>44.3103951350002</v>
-      </c>
-      <c r="J9" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -733,28 +758,31 @@
         <v>46243</v>
       </c>
       <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
         <v>26</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>27</v>
       </c>
-      <c r="D10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10"/>
-      <c r="F10" t="s">
-        <v>13</v>
+      <c r="E10" t="n">
+        <v>1.91884346032829</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.91884346032829</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>6.37537838094154</v>
       </c>
       <c r="H10" t="n">
-        <v>1.91884346032829</v>
-      </c>
-      <c r="I10" t="n">
         <v>41.93872955763</v>
       </c>
-      <c r="J10" t="s">
+      <c r="I10"/>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -763,29 +791,32 @@
         <v>46243</v>
       </c>
       <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
         <v>26</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>27</v>
       </c>
-      <c r="D11" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11"/>
-      <c r="F11" t="s">
+      <c r="E11" t="n">
+        <v>1.91884346032829</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.91884346032829</v>
+      </c>
+      <c r="G11" t="n">
+        <v>6.37537838094154</v>
+      </c>
+      <c r="H11" t="n">
+        <v>41.93872955763</v>
+      </c>
+      <c r="I11"/>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="s">
         <v>15</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.91884346032829</v>
-      </c>
-      <c r="I11" t="n">
-        <v>41.93872955763</v>
-      </c>
-      <c r="J11" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -793,28 +824,31 @@
         <v>46243</v>
       </c>
       <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
         <v>29</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>30</v>
       </c>
-      <c r="D12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12"/>
-      <c r="F12" t="s">
-        <v>13</v>
+      <c r="E12" t="n">
+        <v>-17.4666918131983</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-17.4666918131983</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-12.4707851269817</v>
       </c>
       <c r="H12" t="n">
-        <v>-17.4666918131983</v>
-      </c>
-      <c r="I12" t="n">
         <v>43.0792761429269</v>
       </c>
-      <c r="J12" t="s">
+      <c r="I12"/>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="s">
         <v>14</v>
       </c>
     </row>
@@ -823,29 +857,32 @@
         <v>46243</v>
       </c>
       <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" t="s">
         <v>29</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>30</v>
       </c>
-      <c r="D13" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13"/>
-      <c r="F13" t="s">
+      <c r="E13" t="n">
+        <v>-17.4666918131983</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-17.4666918131983</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-12.4707851269817</v>
+      </c>
+      <c r="H13" t="n">
+        <v>43.0792761429269</v>
+      </c>
+      <c r="I13"/>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="s">
         <v>15</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-17.4666918131983</v>
-      </c>
-      <c r="I13" t="n">
-        <v>43.0792761429269</v>
-      </c>
-      <c r="J13" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRLW_upcoming_projections.xlsx
+++ b/files/NRLW_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -38,6 +38,12 @@
     <t xml:space="preserve">Projected Total</t>
   </si>
   <si>
+    <t xml:space="preserve">Market Period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projection Type</t>
+  </si>
+  <si>
     <t xml:space="preserve">Venue</t>
   </si>
   <si>
@@ -56,7 +62,16 @@
     <t xml:space="preserve">north queensland cowboys</t>
   </si>
   <si>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain (Primary)</t>
+  </si>
+  <si>
     <t xml:space="preserve">No - primary model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted (Reference)</t>
   </si>
   <si>
     <t xml:space="preserve">Reference only - heuristic -0.3 total pts/mm, cap +/-6</t>
@@ -449,9 +464,11 @@
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="16.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="15.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="5.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="16.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="54.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="13.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="28.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="5.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="16.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="54.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -488,19 +505,25 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
         <v>46242</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
         <v>-0.967365923161965</v>
@@ -514,12 +537,18 @@
       <c r="H2" t="n">
         <v>41.1347508280856</v>
       </c>
-      <c r="I2"/>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="s">
-        <v>14</v>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -527,13 +556,13 @@
         <v>46242</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
         <v>-0.967365923161965</v>
@@ -547,12 +576,18 @@
       <c r="H3" t="n">
         <v>41.1347508280856</v>
       </c>
-      <c r="I3"/>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="s">
-        <v>15</v>
+      <c r="I3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -560,13 +595,13 @@
         <v>46242</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E4" t="n">
         <v>2.95591997136961</v>
@@ -580,12 +615,18 @@
       <c r="H4" t="n">
         <v>39.0546153809696</v>
       </c>
-      <c r="I4"/>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="s">
-        <v>14</v>
+      <c r="I4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -593,13 +634,13 @@
         <v>46242</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E5" t="n">
         <v>2.95591997136961</v>
@@ -613,12 +654,18 @@
       <c r="H5" t="n">
         <v>39.0546153809696</v>
       </c>
-      <c r="I5"/>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="s">
-        <v>15</v>
+      <c r="I5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -626,13 +673,13 @@
         <v>46242</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E6" t="n">
         <v>4.30523197794122</v>
@@ -646,12 +693,18 @@
       <c r="H6" t="n">
         <v>39.4395417954011</v>
       </c>
-      <c r="I6"/>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="s">
-        <v>14</v>
+      <c r="I6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -659,13 +712,13 @@
         <v>46242</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E7" t="n">
         <v>4.30523197794122</v>
@@ -679,12 +732,18 @@
       <c r="H7" t="n">
         <v>39.4395417954011</v>
       </c>
-      <c r="I7"/>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="s">
-        <v>15</v>
+      <c r="I7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -692,13 +751,13 @@
         <v>46243</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E8" t="n">
         <v>16.5034438582445</v>
@@ -712,12 +771,18 @@
       <c r="H8" t="n">
         <v>44.3103951350002</v>
       </c>
-      <c r="I8"/>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="s">
-        <v>14</v>
+      <c r="I8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -725,13 +790,13 @@
         <v>46243</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E9" t="n">
         <v>16.5034438582445</v>
@@ -745,12 +810,18 @@
       <c r="H9" t="n">
         <v>44.3103951350002</v>
       </c>
-      <c r="I9"/>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="s">
-        <v>15</v>
+      <c r="I9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K9"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -758,13 +829,13 @@
         <v>46243</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E10" t="n">
         <v>1.91884346032829</v>
@@ -778,12 +849,18 @@
       <c r="H10" t="n">
         <v>41.93872955763</v>
       </c>
-      <c r="I10"/>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="s">
-        <v>14</v>
+      <c r="I10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" t="s">
+        <v>17</v>
+      </c>
+      <c r="K10"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -791,13 +868,13 @@
         <v>46243</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E11" t="n">
         <v>1.91884346032829</v>
@@ -811,12 +888,18 @@
       <c r="H11" t="n">
         <v>41.93872955763</v>
       </c>
-      <c r="I11"/>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="s">
-        <v>15</v>
+      <c r="I11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" t="s">
+        <v>19</v>
+      </c>
+      <c r="K11"/>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -824,13 +907,13 @@
         <v>46243</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E12" t="n">
         <v>-17.4666918131983</v>
@@ -844,12 +927,18 @@
       <c r="H12" t="n">
         <v>43.0792761429269</v>
       </c>
-      <c r="I12"/>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="s">
-        <v>14</v>
+      <c r="I12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K12"/>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -857,13 +946,13 @@
         <v>46243</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E13" t="n">
         <v>-17.4666918131983</v>
@@ -877,12 +966,18 @@
       <c r="H13" t="n">
         <v>43.0792761429269</v>
       </c>
-      <c r="I13"/>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="s">
-        <v>15</v>
+      <c r="I13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" t="s">
+        <v>19</v>
+      </c>
+      <c r="K13"/>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRLW_upcoming_projections.xlsx
+++ b/files/NRLW_upcoming_projections.xlsx
@@ -26,13 +26,13 @@
     <t xml:space="preserve">Away Team</t>
   </si>
   <si>
-    <t xml:space="preserve">Selected / Hybrid Home Line</t>
+    <t xml:space="preserve">Selected / JOINT Home Line</t>
   </si>
   <si>
     <t xml:space="preserve">TEAM Home Line</t>
   </si>
   <si>
-    <t xml:space="preserve">PLAYER Home Line</t>
+    <t xml:space="preserve">JOINT Home Line</t>
   </si>
   <si>
     <t xml:space="preserve">Projected Total</t>
@@ -460,9 +460,9 @@
     <col min="2" max="2" width="5.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="29.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="24.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="27.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="26.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="16.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="15.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="15.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="13.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="28.71" hidden="0" customWidth="1"/>
@@ -526,13 +526,13 @@
         <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.967365923161965</v>
+        <v>-1.18779316771866</v>
       </c>
       <c r="F2" t="n">
         <v>-0.967365923161965</v>
       </c>
       <c r="G2" t="n">
-        <v>0.885127034852399</v>
+        <v>-1.18779316771866</v>
       </c>
       <c r="H2" t="n">
         <v>41.1347508280856</v>
@@ -565,13 +565,13 @@
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.967365923161965</v>
+        <v>-1.18779316771866</v>
       </c>
       <c r="F3" t="n">
         <v>-0.967365923161965</v>
       </c>
       <c r="G3" t="n">
-        <v>0.885127034852399</v>
+        <v>-1.18779316771866</v>
       </c>
       <c r="H3" t="n">
         <v>41.1347508280856</v>
@@ -604,13 +604,13 @@
         <v>23</v>
       </c>
       <c r="E4" t="n">
-        <v>2.95591997136961</v>
+        <v>2.92069172818314</v>
       </c>
       <c r="F4" t="n">
         <v>2.95591997136961</v>
       </c>
       <c r="G4" t="n">
-        <v>6.83914463048428</v>
+        <v>2.92069172818314</v>
       </c>
       <c r="H4" t="n">
         <v>39.0546153809696</v>
@@ -643,13 +643,13 @@
         <v>23</v>
       </c>
       <c r="E5" t="n">
-        <v>2.95591997136961</v>
+        <v>2.92069172818314</v>
       </c>
       <c r="F5" t="n">
         <v>2.95591997136961</v>
       </c>
       <c r="G5" t="n">
-        <v>6.83914463048428</v>
+        <v>2.92069172818314</v>
       </c>
       <c r="H5" t="n">
         <v>39.0546153809696</v>
@@ -682,13 +682,13 @@
         <v>26</v>
       </c>
       <c r="E6" t="n">
-        <v>4.30523197794122</v>
+        <v>1.50319650722794</v>
       </c>
       <c r="F6" t="n">
         <v>4.30523197794122</v>
       </c>
       <c r="G6" t="n">
-        <v>0.754367052351461</v>
+        <v>1.50319650722794</v>
       </c>
       <c r="H6" t="n">
         <v>39.4395417954011</v>
@@ -721,13 +721,13 @@
         <v>26</v>
       </c>
       <c r="E7" t="n">
-        <v>4.30523197794122</v>
+        <v>1.50319650722794</v>
       </c>
       <c r="F7" t="n">
         <v>4.30523197794122</v>
       </c>
       <c r="G7" t="n">
-        <v>0.754367052351461</v>
+        <v>1.50319650722794</v>
       </c>
       <c r="H7" t="n">
         <v>39.4395417954011</v>
@@ -760,13 +760,13 @@
         <v>29</v>
       </c>
       <c r="E8" t="n">
-        <v>16.5034438582445</v>
+        <v>20.655839953819</v>
       </c>
       <c r="F8" t="n">
         <v>16.5034438582445</v>
       </c>
       <c r="G8" t="n">
-        <v>10.2754320846569</v>
+        <v>20.655839953819</v>
       </c>
       <c r="H8" t="n">
         <v>44.3103951350002</v>
@@ -799,13 +799,13 @@
         <v>29</v>
       </c>
       <c r="E9" t="n">
-        <v>16.5034438582445</v>
+        <v>20.655839953819</v>
       </c>
       <c r="F9" t="n">
         <v>16.5034438582445</v>
       </c>
       <c r="G9" t="n">
-        <v>10.2754320846569</v>
+        <v>20.655839953819</v>
       </c>
       <c r="H9" t="n">
         <v>44.3103951350002</v>
@@ -838,13 +838,13 @@
         <v>32</v>
       </c>
       <c r="E10" t="n">
-        <v>1.91884346032829</v>
+        <v>1.50547993714263</v>
       </c>
       <c r="F10" t="n">
         <v>1.91884346032829</v>
       </c>
       <c r="G10" t="n">
-        <v>6.37537838094154</v>
+        <v>1.50547993714263</v>
       </c>
       <c r="H10" t="n">
         <v>41.93872955763</v>
@@ -877,13 +877,13 @@
         <v>32</v>
       </c>
       <c r="E11" t="n">
-        <v>1.91884346032829</v>
+        <v>1.50547993714263</v>
       </c>
       <c r="F11" t="n">
         <v>1.91884346032829</v>
       </c>
       <c r="G11" t="n">
-        <v>6.37537838094154</v>
+        <v>1.50547993714263</v>
       </c>
       <c r="H11" t="n">
         <v>41.93872955763</v>
@@ -916,13 +916,13 @@
         <v>35</v>
       </c>
       <c r="E12" t="n">
-        <v>-17.4666918131983</v>
+        <v>-22.4168624650619</v>
       </c>
       <c r="F12" t="n">
         <v>-17.4666918131983</v>
       </c>
       <c r="G12" t="n">
-        <v>-12.4707851269817</v>
+        <v>-22.4168624650619</v>
       </c>
       <c r="H12" t="n">
         <v>43.0792761429269</v>
@@ -955,13 +955,13 @@
         <v>35</v>
       </c>
       <c r="E13" t="n">
-        <v>-17.4666918131983</v>
+        <v>-22.4168624650619</v>
       </c>
       <c r="F13" t="n">
         <v>-17.4666918131983</v>
       </c>
       <c r="G13" t="n">
-        <v>-12.4707851269817</v>
+        <v>-22.4168624650619</v>
       </c>
       <c r="H13" t="n">
         <v>43.0792761429269</v>

--- a/files/NRLW_upcoming_projections.xlsx
+++ b/files/NRLW_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -53,73 +53,70 @@
     <t xml:space="preserve">Weather Applied</t>
   </si>
   <si>
+    <t xml:space="preserve">17:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain (Primary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No - primary model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted (Reference)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference only - heuristic -0.3 total pts/mm, cap +/-6</t>
+  </si>
+  <si>
     <t xml:space="preserve">12:45</t>
   </si>
   <si>
-    <t xml:space="preserve">canterbury bankstown bulldogs</t>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:15</t>
   </si>
   <si>
     <t xml:space="preserve">north queensland cowboys</t>
   </si>
   <si>
-    <t xml:space="preserve">FT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain (Primary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No - primary model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted (Reference)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference only - heuristic -0.3 total pts/mm, cap +/-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:15</t>
-  </si>
-  <si>
     <t xml:space="preserve">cronulla-sutherland sharks</t>
   </si>
   <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:15</t>
+    <t xml:space="preserve">13:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wests tigers</t>
   </si>
   <si>
     <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
   </si>
 </sst>
 </file>
@@ -458,8 +455,8 @@
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="5.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="29.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="24.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="24.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="27.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="26.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="15.71" hidden="0" customWidth="1"/>
@@ -514,7 +511,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46242</v>
+        <v>46249</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
@@ -526,16 +523,16 @@
         <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.18779316771866</v>
+        <v>5.69623437396441</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.967365923161965</v>
+        <v>1.24751786165426</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.18779316771866</v>
+        <v>5.69623437396441</v>
       </c>
       <c r="H2" t="n">
-        <v>41.1347508280856</v>
+        <v>43.6816211575459</v>
       </c>
       <c r="I2" t="s">
         <v>16</v>
@@ -553,7 +550,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46242</v>
+        <v>46249</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -565,16 +562,16 @@
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.18779316771866</v>
+        <v>5.69623437396441</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.967365923161965</v>
+        <v>1.24751786165426</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.18779316771866</v>
+        <v>5.69623437396441</v>
       </c>
       <c r="H3" t="n">
-        <v>41.1347508280856</v>
+        <v>43.6816211575459</v>
       </c>
       <c r="I3" t="s">
         <v>16</v>
@@ -592,7 +589,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46242</v>
+        <v>46249</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
@@ -604,16 +601,16 @@
         <v>23</v>
       </c>
       <c r="E4" t="n">
-        <v>2.92069172818314</v>
+        <v>-13.6325979368923</v>
       </c>
       <c r="F4" t="n">
-        <v>2.95591997136961</v>
+        <v>-11.4393181893186</v>
       </c>
       <c r="G4" t="n">
-        <v>2.92069172818314</v>
+        <v>-13.6325979368923</v>
       </c>
       <c r="H4" t="n">
-        <v>39.0546153809696</v>
+        <v>37.3199806642968</v>
       </c>
       <c r="I4" t="s">
         <v>16</v>
@@ -631,7 +628,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46242</v>
+        <v>46249</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
@@ -643,16 +640,16 @@
         <v>23</v>
       </c>
       <c r="E5" t="n">
-        <v>2.92069172818314</v>
+        <v>-13.6325979368923</v>
       </c>
       <c r="F5" t="n">
-        <v>2.95591997136961</v>
+        <v>-11.4393181893186</v>
       </c>
       <c r="G5" t="n">
-        <v>2.92069172818314</v>
+        <v>-13.6325979368923</v>
       </c>
       <c r="H5" t="n">
-        <v>39.0546153809696</v>
+        <v>37.3199806642968</v>
       </c>
       <c r="I5" t="s">
         <v>16</v>
@@ -670,7 +667,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46242</v>
+        <v>46249</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -679,19 +676,19 @@
         <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>1.50319650722794</v>
+        <v>17.9701142777633</v>
       </c>
       <c r="F6" t="n">
-        <v>4.30523197794122</v>
+        <v>19.7784829104098</v>
       </c>
       <c r="G6" t="n">
-        <v>1.50319650722794</v>
+        <v>17.9701142777633</v>
       </c>
       <c r="H6" t="n">
-        <v>39.4395417954011</v>
+        <v>42.4539701075464</v>
       </c>
       <c r="I6" t="s">
         <v>16</v>
@@ -709,7 +706,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46242</v>
+        <v>46249</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
@@ -718,19 +715,19 @@
         <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>1.50319650722794</v>
+        <v>17.9701142777633</v>
       </c>
       <c r="F7" t="n">
-        <v>4.30523197794122</v>
+        <v>19.7784829104098</v>
       </c>
       <c r="G7" t="n">
-        <v>1.50319650722794</v>
+        <v>17.9701142777633</v>
       </c>
       <c r="H7" t="n">
-        <v>39.4395417954011</v>
+        <v>42.4539701075464</v>
       </c>
       <c r="I7" t="s">
         <v>16</v>
@@ -748,28 +745,28 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46243</v>
+        <v>46250</v>
       </c>
       <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
         <v>27</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>28</v>
       </c>
-      <c r="D8" t="s">
-        <v>29</v>
-      </c>
       <c r="E8" t="n">
-        <v>20.655839953819</v>
+        <v>-6.93666763909937</v>
       </c>
       <c r="F8" t="n">
-        <v>16.5034438582445</v>
+        <v>-2.30265945684589</v>
       </c>
       <c r="G8" t="n">
-        <v>20.655839953819</v>
+        <v>-6.93666763909937</v>
       </c>
       <c r="H8" t="n">
-        <v>44.3103951350002</v>
+        <v>39.5139284147171</v>
       </c>
       <c r="I8" t="s">
         <v>16</v>
@@ -787,28 +784,28 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46243</v>
+        <v>46250</v>
       </c>
       <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
         <v>27</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>28</v>
       </c>
-      <c r="D9" t="s">
-        <v>29</v>
-      </c>
       <c r="E9" t="n">
-        <v>20.655839953819</v>
+        <v>-6.93666763909937</v>
       </c>
       <c r="F9" t="n">
-        <v>16.5034438582445</v>
+        <v>-2.30265945684589</v>
       </c>
       <c r="G9" t="n">
-        <v>20.655839953819</v>
+        <v>-6.93666763909937</v>
       </c>
       <c r="H9" t="n">
-        <v>44.3103951350002</v>
+        <v>39.5139284147171</v>
       </c>
       <c r="I9" t="s">
         <v>16</v>
@@ -826,28 +823,28 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46243</v>
+        <v>46250</v>
       </c>
       <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
         <v>30</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>31</v>
       </c>
-      <c r="D10" t="s">
-        <v>32</v>
-      </c>
       <c r="E10" t="n">
-        <v>1.50547993714263</v>
+        <v>6.01108703652623</v>
       </c>
       <c r="F10" t="n">
-        <v>1.91884346032829</v>
+        <v>6.84176522772164</v>
       </c>
       <c r="G10" t="n">
-        <v>1.50547993714263</v>
+        <v>6.01108703652623</v>
       </c>
       <c r="H10" t="n">
-        <v>41.93872955763</v>
+        <v>38.4893634117312</v>
       </c>
       <c r="I10" t="s">
         <v>16</v>
@@ -865,28 +862,28 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46243</v>
+        <v>46250</v>
       </c>
       <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
         <v>30</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>31</v>
       </c>
-      <c r="D11" t="s">
-        <v>32</v>
-      </c>
       <c r="E11" t="n">
-        <v>1.50547993714263</v>
+        <v>6.01108703652623</v>
       </c>
       <c r="F11" t="n">
-        <v>1.91884346032829</v>
+        <v>6.84176522772164</v>
       </c>
       <c r="G11" t="n">
-        <v>1.50547993714263</v>
+        <v>6.01108703652623</v>
       </c>
       <c r="H11" t="n">
-        <v>41.93872955763</v>
+        <v>38.4893634117312</v>
       </c>
       <c r="I11" t="s">
         <v>16</v>
@@ -904,28 +901,28 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46243</v>
+        <v>46250</v>
       </c>
       <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
         <v>33</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>34</v>
       </c>
-      <c r="D12" t="s">
-        <v>35</v>
-      </c>
       <c r="E12" t="n">
-        <v>-22.4168624650619</v>
+        <v>10.3668352661858</v>
       </c>
       <c r="F12" t="n">
-        <v>-17.4666918131983</v>
+        <v>8.13850789991952</v>
       </c>
       <c r="G12" t="n">
-        <v>-22.4168624650619</v>
+        <v>10.3668352661858</v>
       </c>
       <c r="H12" t="n">
-        <v>43.0792761429269</v>
+        <v>41.9040563084958</v>
       </c>
       <c r="I12" t="s">
         <v>16</v>
@@ -943,28 +940,28 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46243</v>
+        <v>46250</v>
       </c>
       <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
         <v>33</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>34</v>
       </c>
-      <c r="D13" t="s">
-        <v>35</v>
-      </c>
       <c r="E13" t="n">
-        <v>-22.4168624650619</v>
+        <v>10.3668352661858</v>
       </c>
       <c r="F13" t="n">
-        <v>-17.4666918131983</v>
+        <v>8.13850789991952</v>
       </c>
       <c r="G13" t="n">
-        <v>-22.4168624650619</v>
+        <v>10.3668352661858</v>
       </c>
       <c r="H13" t="n">
-        <v>43.0792761429269</v>
+        <v>41.9040563084958</v>
       </c>
       <c r="I13" t="s">
         <v>16</v>

--- a/files/NRLW_upcoming_projections.xlsx
+++ b/files/NRLW_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury bankstown bulldogs</t>
   </si>
   <si>
     <t xml:space="preserve">11:50</t>
@@ -456,7 +459,7 @@
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="5.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="24.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="27.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="29.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="26.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="15.71" hidden="0" customWidth="1"/>
@@ -523,13 +526,13 @@
         <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>5.69623437396441</v>
+        <v>-3.64083584466667</v>
       </c>
       <c r="F2" t="n">
         <v>1.24751786165426</v>
       </c>
       <c r="G2" t="n">
-        <v>5.69623437396441</v>
+        <v>-3.64083584466667</v>
       </c>
       <c r="H2" t="n">
         <v>43.6816211575459</v>
@@ -562,13 +565,13 @@
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>5.69623437396441</v>
+        <v>-3.64083584466667</v>
       </c>
       <c r="F3" t="n">
         <v>1.24751786165426</v>
       </c>
       <c r="G3" t="n">
-        <v>5.69623437396441</v>
+        <v>-3.64083584466667</v>
       </c>
       <c r="H3" t="n">
         <v>43.6816211575459</v>
@@ -601,13 +604,13 @@
         <v>23</v>
       </c>
       <c r="E4" t="n">
-        <v>-13.6325979368923</v>
+        <v>-10.6122942592167</v>
       </c>
       <c r="F4" t="n">
         <v>-11.4393181893186</v>
       </c>
       <c r="G4" t="n">
-        <v>-13.6325979368923</v>
+        <v>-10.6122942592167</v>
       </c>
       <c r="H4" t="n">
         <v>37.3199806642968</v>
@@ -640,13 +643,13 @@
         <v>23</v>
       </c>
       <c r="E5" t="n">
-        <v>-13.6325979368923</v>
+        <v>-10.6122942592167</v>
       </c>
       <c r="F5" t="n">
         <v>-11.4393181893186</v>
       </c>
       <c r="G5" t="n">
-        <v>-13.6325979368923</v>
+        <v>-10.6122942592167</v>
       </c>
       <c r="H5" t="n">
         <v>37.3199806642968</v>
@@ -676,19 +679,19 @@
         <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E6" t="n">
-        <v>17.9701142777633</v>
+        <v>-0.303299907704426</v>
       </c>
       <c r="F6" t="n">
-        <v>19.7784829104098</v>
+        <v>1.87340666767035</v>
       </c>
       <c r="G6" t="n">
-        <v>17.9701142777633</v>
+        <v>-0.303299907704426</v>
       </c>
       <c r="H6" t="n">
-        <v>42.4539701075464</v>
+        <v>43.4627773245169</v>
       </c>
       <c r="I6" t="s">
         <v>16</v>
@@ -715,19 +718,19 @@
         <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E7" t="n">
-        <v>17.9701142777633</v>
+        <v>-0.303299907704426</v>
       </c>
       <c r="F7" t="n">
-        <v>19.7784829104098</v>
+        <v>1.87340666767035</v>
       </c>
       <c r="G7" t="n">
-        <v>17.9701142777633</v>
+        <v>-0.303299907704426</v>
       </c>
       <c r="H7" t="n">
-        <v>42.4539701075464</v>
+        <v>43.4627773245169</v>
       </c>
       <c r="I7" t="s">
         <v>16</v>
@@ -748,22 +751,22 @@
         <v>46250</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E8" t="n">
-        <v>-6.93666763909937</v>
+        <v>-8.58734343837506</v>
       </c>
       <c r="F8" t="n">
         <v>-2.30265945684589</v>
       </c>
       <c r="G8" t="n">
-        <v>-6.93666763909937</v>
+        <v>-8.58734343837506</v>
       </c>
       <c r="H8" t="n">
         <v>39.5139284147171</v>
@@ -787,22 +790,22 @@
         <v>46250</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.93666763909937</v>
+        <v>-8.58734343837506</v>
       </c>
       <c r="F9" t="n">
         <v>-2.30265945684589</v>
       </c>
       <c r="G9" t="n">
-        <v>-6.93666763909937</v>
+        <v>-8.58734343837506</v>
       </c>
       <c r="H9" t="n">
         <v>39.5139284147171</v>
@@ -826,22 +829,22 @@
         <v>46250</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E10" t="n">
-        <v>6.01108703652623</v>
+        <v>8.81765713502072</v>
       </c>
       <c r="F10" t="n">
         <v>6.84176522772164</v>
       </c>
       <c r="G10" t="n">
-        <v>6.01108703652623</v>
+        <v>8.81765713502072</v>
       </c>
       <c r="H10" t="n">
         <v>38.4893634117312</v>
@@ -865,22 +868,22 @@
         <v>46250</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E11" t="n">
-        <v>6.01108703652623</v>
+        <v>8.81765713502072</v>
       </c>
       <c r="F11" t="n">
         <v>6.84176522772164</v>
       </c>
       <c r="G11" t="n">
-        <v>6.01108703652623</v>
+        <v>8.81765713502072</v>
       </c>
       <c r="H11" t="n">
         <v>38.4893634117312</v>
@@ -904,22 +907,22 @@
         <v>46250</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E12" t="n">
-        <v>10.3668352661858</v>
+        <v>13.045042476135</v>
       </c>
       <c r="F12" t="n">
         <v>8.13850789991952</v>
       </c>
       <c r="G12" t="n">
-        <v>10.3668352661858</v>
+        <v>13.045042476135</v>
       </c>
       <c r="H12" t="n">
         <v>41.9040563084958</v>
@@ -943,22 +946,22 @@
         <v>46250</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E13" t="n">
-        <v>10.3668352661858</v>
+        <v>13.045042476135</v>
       </c>
       <c r="F13" t="n">
         <v>8.13850789991952</v>
       </c>
       <c r="G13" t="n">
-        <v>10.3668352661858</v>
+        <v>13.045042476135</v>
       </c>
       <c r="H13" t="n">
         <v>41.9040563084958</v>

--- a/files/NRLW_upcoming_projections.xlsx
+++ b/files/NRLW_upcoming_projections.xlsx
@@ -526,13 +526,13 @@
         <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.64083584466667</v>
+        <v>2.7840755210995</v>
       </c>
       <c r="F2" t="n">
         <v>1.24751786165426</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.64083584466667</v>
+        <v>2.7840755210995</v>
       </c>
       <c r="H2" t="n">
         <v>43.6816211575459</v>
@@ -565,13 +565,13 @@
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.64083584466667</v>
+        <v>2.7840755210995</v>
       </c>
       <c r="F3" t="n">
         <v>1.24751786165426</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.64083584466667</v>
+        <v>2.7840755210995</v>
       </c>
       <c r="H3" t="n">
         <v>43.6816211575459</v>
@@ -604,13 +604,13 @@
         <v>23</v>
       </c>
       <c r="E4" t="n">
-        <v>-10.6122942592167</v>
+        <v>-11.2167455826204</v>
       </c>
       <c r="F4" t="n">
         <v>-11.4393181893186</v>
       </c>
       <c r="G4" t="n">
-        <v>-10.6122942592167</v>
+        <v>-11.2167455826204</v>
       </c>
       <c r="H4" t="n">
         <v>37.3199806642968</v>
@@ -643,13 +643,13 @@
         <v>23</v>
       </c>
       <c r="E5" t="n">
-        <v>-10.6122942592167</v>
+        <v>-11.2167455826204</v>
       </c>
       <c r="F5" t="n">
         <v>-11.4393181893186</v>
       </c>
       <c r="G5" t="n">
-        <v>-10.6122942592167</v>
+        <v>-11.2167455826204</v>
       </c>
       <c r="H5" t="n">
         <v>37.3199806642968</v>
@@ -682,13 +682,13 @@
         <v>26</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.303299907704426</v>
+        <v>0.00270974736576157</v>
       </c>
       <c r="F6" t="n">
         <v>1.87340666767035</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.303299907704426</v>
+        <v>0.00270974736576157</v>
       </c>
       <c r="H6" t="n">
         <v>43.4627773245169</v>
@@ -721,13 +721,13 @@
         <v>26</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.303299907704426</v>
+        <v>0.00270974736576157</v>
       </c>
       <c r="F7" t="n">
         <v>1.87340666767035</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.303299907704426</v>
+        <v>0.00270974736576157</v>
       </c>
       <c r="H7" t="n">
         <v>43.4627773245169</v>
@@ -760,13 +760,13 @@
         <v>29</v>
       </c>
       <c r="E8" t="n">
-        <v>-8.58734343837506</v>
+        <v>-5.29954896215484</v>
       </c>
       <c r="F8" t="n">
         <v>-2.30265945684589</v>
       </c>
       <c r="G8" t="n">
-        <v>-8.58734343837506</v>
+        <v>-5.29954896215484</v>
       </c>
       <c r="H8" t="n">
         <v>39.5139284147171</v>
@@ -799,13 +799,13 @@
         <v>29</v>
       </c>
       <c r="E9" t="n">
-        <v>-8.58734343837506</v>
+        <v>-5.29954896215484</v>
       </c>
       <c r="F9" t="n">
         <v>-2.30265945684589</v>
       </c>
       <c r="G9" t="n">
-        <v>-8.58734343837506</v>
+        <v>-5.29954896215484</v>
       </c>
       <c r="H9" t="n">
         <v>39.5139284147171</v>
@@ -838,13 +838,13 @@
         <v>32</v>
       </c>
       <c r="E10" t="n">
-        <v>8.81765713502072</v>
+        <v>8.82579315695334</v>
       </c>
       <c r="F10" t="n">
         <v>6.84176522772164</v>
       </c>
       <c r="G10" t="n">
-        <v>8.81765713502072</v>
+        <v>8.82579315695334</v>
       </c>
       <c r="H10" t="n">
         <v>38.4893634117312</v>
@@ -877,13 +877,13 @@
         <v>32</v>
       </c>
       <c r="E11" t="n">
-        <v>8.81765713502072</v>
+        <v>8.82579315695334</v>
       </c>
       <c r="F11" t="n">
         <v>6.84176522772164</v>
       </c>
       <c r="G11" t="n">
-        <v>8.81765713502072</v>
+        <v>8.82579315695334</v>
       </c>
       <c r="H11" t="n">
         <v>38.4893634117312</v>
@@ -916,13 +916,13 @@
         <v>35</v>
       </c>
       <c r="E12" t="n">
-        <v>13.045042476135</v>
+        <v>15.487981534724</v>
       </c>
       <c r="F12" t="n">
         <v>8.13850789991952</v>
       </c>
       <c r="G12" t="n">
-        <v>13.045042476135</v>
+        <v>15.487981534724</v>
       </c>
       <c r="H12" t="n">
         <v>41.9040563084958</v>
@@ -955,13 +955,13 @@
         <v>35</v>
       </c>
       <c r="E13" t="n">
-        <v>13.045042476135</v>
+        <v>15.487981534724</v>
       </c>
       <c r="F13" t="n">
         <v>8.13850789991952</v>
       </c>
       <c r="G13" t="n">
-        <v>13.045042476135</v>
+        <v>15.487981534724</v>
       </c>
       <c r="H13" t="n">
         <v>41.9040563084958</v>

--- a/files/NRLW_upcoming_projections.xlsx
+++ b/files/NRLW_upcoming_projections.xlsx
@@ -53,70 +53,70 @@
     <t xml:space="preserve">Weather Applied</t>
   </si>
   <si>
+    <t xml:space="preserve">15:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain (Primary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No - primary model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted (Reference)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference only - heuristic -0.3 total pts/mm, cap +/-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wests tigers</t>
+  </si>
+  <si>
     <t xml:space="preserve">17:15</t>
   </si>
   <si>
+    <t xml:space="preserve">st george illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
     <t xml:space="preserve">brisbane broncos</t>
   </si>
   <si>
+    <t xml:space="preserve">13:45</t>
+  </si>
+  <si>
     <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain (Primary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No - primary model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted (Reference)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference only - heuristic -0.3 total pts/mm, cap +/-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
   </si>
   <si>
     <t xml:space="preserve">warriors</t>
@@ -458,8 +458,8 @@
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="5.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="24.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="29.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="29.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="24.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="26.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="15.71" hidden="0" customWidth="1"/>
@@ -514,7 +514,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46249</v>
+        <v>46256</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
@@ -526,16 +526,16 @@
         <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7840755210995</v>
+        <v>9.30218626611973</v>
       </c>
       <c r="F2" t="n">
-        <v>1.24751786165426</v>
+        <v>9.14436818066069</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7840755210995</v>
+        <v>9.30218626611973</v>
       </c>
       <c r="H2" t="n">
-        <v>43.6816211575459</v>
+        <v>44.8254752081875</v>
       </c>
       <c r="I2" t="s">
         <v>16</v>
@@ -553,7 +553,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46249</v>
+        <v>46256</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -565,16 +565,16 @@
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7840755210995</v>
+        <v>9.30218626611973</v>
       </c>
       <c r="F3" t="n">
-        <v>1.24751786165426</v>
+        <v>9.14436818066069</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7840755210995</v>
+        <v>9.30218626611973</v>
       </c>
       <c r="H3" t="n">
-        <v>43.6816211575459</v>
+        <v>44.8254752081875</v>
       </c>
       <c r="I3" t="s">
         <v>16</v>
@@ -592,7 +592,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46249</v>
+        <v>46256</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
@@ -604,16 +604,16 @@
         <v>23</v>
       </c>
       <c r="E4" t="n">
-        <v>-11.2167455826204</v>
+        <v>-10.1191034061516</v>
       </c>
       <c r="F4" t="n">
-        <v>-11.4393181893186</v>
+        <v>-8.55778847280921</v>
       </c>
       <c r="G4" t="n">
-        <v>-11.2167455826204</v>
+        <v>-10.1191034061516</v>
       </c>
       <c r="H4" t="n">
-        <v>37.3199806642968</v>
+        <v>43.5101752823477</v>
       </c>
       <c r="I4" t="s">
         <v>16</v>
@@ -631,7 +631,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46249</v>
+        <v>46256</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
@@ -643,16 +643,16 @@
         <v>23</v>
       </c>
       <c r="E5" t="n">
-        <v>-11.2167455826204</v>
+        <v>-10.1191034061516</v>
       </c>
       <c r="F5" t="n">
-        <v>-11.4393181893186</v>
+        <v>-8.55778847280921</v>
       </c>
       <c r="G5" t="n">
-        <v>-11.2167455826204</v>
+        <v>-10.1191034061516</v>
       </c>
       <c r="H5" t="n">
-        <v>37.3199806642968</v>
+        <v>43.5101752823477</v>
       </c>
       <c r="I5" t="s">
         <v>16</v>
@@ -670,7 +670,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46249</v>
+        <v>46256</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -682,16 +682,16 @@
         <v>26</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00270974736576157</v>
+        <v>1.23653397868303</v>
       </c>
       <c r="F6" t="n">
-        <v>1.87340666767035</v>
+        <v>2.04591225597056</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00270974736576157</v>
+        <v>1.23653397868303</v>
       </c>
       <c r="H6" t="n">
-        <v>43.4627773245169</v>
+        <v>39.0964124200242</v>
       </c>
       <c r="I6" t="s">
         <v>16</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46249</v>
+        <v>46256</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
@@ -721,16 +721,16 @@
         <v>26</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00270974736576157</v>
+        <v>1.23653397868303</v>
       </c>
       <c r="F7" t="n">
-        <v>1.87340666767035</v>
+        <v>2.04591225597056</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00270974736576157</v>
+        <v>1.23653397868303</v>
       </c>
       <c r="H7" t="n">
-        <v>43.4627773245169</v>
+        <v>39.0964124200242</v>
       </c>
       <c r="I7" t="s">
         <v>16</v>
@@ -748,7 +748,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46250</v>
+        <v>46257</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
@@ -760,16 +760,16 @@
         <v>29</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.29954896215484</v>
+        <v>-1.26251679155279</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.30265945684589</v>
+        <v>-4.50377486850017</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.29954896215484</v>
+        <v>-1.26251679155279</v>
       </c>
       <c r="H8" t="n">
-        <v>39.5139284147171</v>
+        <v>41.0357964870386</v>
       </c>
       <c r="I8" t="s">
         <v>16</v>
@@ -787,7 +787,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46250</v>
+        <v>46257</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
@@ -799,16 +799,16 @@
         <v>29</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.29954896215484</v>
+        <v>-1.26251679155279</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.30265945684589</v>
+        <v>-4.50377486850017</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.29954896215484</v>
+        <v>-1.26251679155279</v>
       </c>
       <c r="H9" t="n">
-        <v>39.5139284147171</v>
+        <v>41.0357964870386</v>
       </c>
       <c r="I9" t="s">
         <v>16</v>
@@ -826,7 +826,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46250</v>
+        <v>46257</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
@@ -838,16 +838,16 @@
         <v>32</v>
       </c>
       <c r="E10" t="n">
-        <v>8.82579315695334</v>
+        <v>9.67950514355656</v>
       </c>
       <c r="F10" t="n">
-        <v>6.84176522772164</v>
+        <v>7.48263222765156</v>
       </c>
       <c r="G10" t="n">
-        <v>8.82579315695334</v>
+        <v>9.67950514355656</v>
       </c>
       <c r="H10" t="n">
-        <v>38.4893634117312</v>
+        <v>42.8875078910283</v>
       </c>
       <c r="I10" t="s">
         <v>16</v>
@@ -865,7 +865,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46250</v>
+        <v>46257</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
@@ -877,16 +877,16 @@
         <v>32</v>
       </c>
       <c r="E11" t="n">
-        <v>8.82579315695334</v>
+        <v>9.67950514355656</v>
       </c>
       <c r="F11" t="n">
-        <v>6.84176522772164</v>
+        <v>7.48263222765156</v>
       </c>
       <c r="G11" t="n">
-        <v>8.82579315695334</v>
+        <v>9.67950514355656</v>
       </c>
       <c r="H11" t="n">
-        <v>38.4893634117312</v>
+        <v>42.8875078910283</v>
       </c>
       <c r="I11" t="s">
         <v>16</v>
@@ -904,7 +904,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46250</v>
+        <v>46257</v>
       </c>
       <c r="B12" t="s">
         <v>33</v>
@@ -916,16 +916,16 @@
         <v>35</v>
       </c>
       <c r="E12" t="n">
-        <v>15.487981534724</v>
+        <v>-10.6256691072607</v>
       </c>
       <c r="F12" t="n">
-        <v>8.13850789991952</v>
+        <v>-13.1994092539009</v>
       </c>
       <c r="G12" t="n">
-        <v>15.487981534724</v>
+        <v>-10.6256691072607</v>
       </c>
       <c r="H12" t="n">
-        <v>41.9040563084958</v>
+        <v>44.3871229917024</v>
       </c>
       <c r="I12" t="s">
         <v>16</v>
@@ -943,7 +943,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46250</v>
+        <v>46257</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
@@ -955,16 +955,16 @@
         <v>35</v>
       </c>
       <c r="E13" t="n">
-        <v>15.487981534724</v>
+        <v>-10.6256691072607</v>
       </c>
       <c r="F13" t="n">
-        <v>8.13850789991952</v>
+        <v>-13.1994092539009</v>
       </c>
       <c r="G13" t="n">
-        <v>15.487981534724</v>
+        <v>-10.6256691072607</v>
       </c>
       <c r="H13" t="n">
-        <v>41.9040563084958</v>
+        <v>44.3871229917024</v>
       </c>
       <c r="I13" t="s">
         <v>16</v>

--- a/files/NRLW_upcoming_projections.xlsx
+++ b/files/NRLW_upcoming_projections.xlsx
@@ -526,13 +526,13 @@
         <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>9.30218626611973</v>
+        <v>10.7679343340717</v>
       </c>
       <c r="F2" t="n">
         <v>9.14436818066069</v>
       </c>
       <c r="G2" t="n">
-        <v>9.30218626611973</v>
+        <v>10.7679343340717</v>
       </c>
       <c r="H2" t="n">
         <v>44.8254752081875</v>
@@ -565,13 +565,13 @@
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>9.30218626611973</v>
+        <v>10.7679343340717</v>
       </c>
       <c r="F3" t="n">
         <v>9.14436818066069</v>
       </c>
       <c r="G3" t="n">
-        <v>9.30218626611973</v>
+        <v>10.7679343340717</v>
       </c>
       <c r="H3" t="n">
         <v>44.8254752081875</v>
@@ -604,13 +604,13 @@
         <v>23</v>
       </c>
       <c r="E4" t="n">
-        <v>-10.1191034061516</v>
+        <v>-10.4748910736777</v>
       </c>
       <c r="F4" t="n">
         <v>-8.55778847280921</v>
       </c>
       <c r="G4" t="n">
-        <v>-10.1191034061516</v>
+        <v>-10.4748910736777</v>
       </c>
       <c r="H4" t="n">
         <v>43.5101752823477</v>
@@ -643,13 +643,13 @@
         <v>23</v>
       </c>
       <c r="E5" t="n">
-        <v>-10.1191034061516</v>
+        <v>-10.4748910736777</v>
       </c>
       <c r="F5" t="n">
         <v>-8.55778847280921</v>
       </c>
       <c r="G5" t="n">
-        <v>-10.1191034061516</v>
+        <v>-10.4748910736777</v>
       </c>
       <c r="H5" t="n">
         <v>43.5101752823477</v>
@@ -682,13 +682,13 @@
         <v>26</v>
       </c>
       <c r="E6" t="n">
-        <v>1.23653397868303</v>
+        <v>0.127558722602551</v>
       </c>
       <c r="F6" t="n">
         <v>2.04591225597056</v>
       </c>
       <c r="G6" t="n">
-        <v>1.23653397868303</v>
+        <v>0.127558722602551</v>
       </c>
       <c r="H6" t="n">
         <v>39.0964124200242</v>
@@ -721,13 +721,13 @@
         <v>26</v>
       </c>
       <c r="E7" t="n">
-        <v>1.23653397868303</v>
+        <v>0.127558722602551</v>
       </c>
       <c r="F7" t="n">
         <v>2.04591225597056</v>
       </c>
       <c r="G7" t="n">
-        <v>1.23653397868303</v>
+        <v>0.127558722602551</v>
       </c>
       <c r="H7" t="n">
         <v>39.0964124200242</v>
@@ -760,13 +760,13 @@
         <v>29</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.26251679155279</v>
+        <v>-4.72619030904951</v>
       </c>
       <c r="F8" t="n">
         <v>-4.50377486850017</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.26251679155279</v>
+        <v>-4.72619030904951</v>
       </c>
       <c r="H8" t="n">
         <v>41.0357964870386</v>
@@ -799,13 +799,13 @@
         <v>29</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.26251679155279</v>
+        <v>-4.72619030904951</v>
       </c>
       <c r="F9" t="n">
         <v>-4.50377486850017</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.26251679155279</v>
+        <v>-4.72619030904951</v>
       </c>
       <c r="H9" t="n">
         <v>41.0357964870386</v>
@@ -838,13 +838,13 @@
         <v>32</v>
       </c>
       <c r="E10" t="n">
-        <v>9.67950514355656</v>
+        <v>10.687527216143</v>
       </c>
       <c r="F10" t="n">
         <v>7.48263222765156</v>
       </c>
       <c r="G10" t="n">
-        <v>9.67950514355656</v>
+        <v>10.687527216143</v>
       </c>
       <c r="H10" t="n">
         <v>42.8875078910283</v>
@@ -877,13 +877,13 @@
         <v>32</v>
       </c>
       <c r="E11" t="n">
-        <v>9.67950514355656</v>
+        <v>10.687527216143</v>
       </c>
       <c r="F11" t="n">
         <v>7.48263222765156</v>
       </c>
       <c r="G11" t="n">
-        <v>9.67950514355656</v>
+        <v>10.687527216143</v>
       </c>
       <c r="H11" t="n">
         <v>42.8875078910283</v>
@@ -916,13 +916,13 @@
         <v>35</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.6256691072607</v>
+        <v>-10.9684320847818</v>
       </c>
       <c r="F12" t="n">
         <v>-13.1994092539009</v>
       </c>
       <c r="G12" t="n">
-        <v>-10.6256691072607</v>
+        <v>-10.9684320847818</v>
       </c>
       <c r="H12" t="n">
         <v>44.3871229917024</v>
@@ -955,13 +955,13 @@
         <v>35</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.6256691072607</v>
+        <v>-10.9684320847818</v>
       </c>
       <c r="F13" t="n">
         <v>-13.1994092539009</v>
       </c>
       <c r="G13" t="n">
-        <v>-10.6256691072607</v>
+        <v>-10.9684320847818</v>
       </c>
       <c r="H13" t="n">
         <v>44.3871229917024</v>

--- a/files/NRLW_upcoming_projections.xlsx
+++ b/files/NRLW_upcoming_projections.xlsx
@@ -526,13 +526,13 @@
         <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>10.7679343340717</v>
+        <v>11.5118176569163</v>
       </c>
       <c r="F2" t="n">
         <v>9.14436818066069</v>
       </c>
       <c r="G2" t="n">
-        <v>10.7679343340717</v>
+        <v>11.5118176569163</v>
       </c>
       <c r="H2" t="n">
         <v>44.8254752081875</v>
@@ -565,13 +565,13 @@
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>10.7679343340717</v>
+        <v>11.5118176569163</v>
       </c>
       <c r="F3" t="n">
         <v>9.14436818066069</v>
       </c>
       <c r="G3" t="n">
-        <v>10.7679343340717</v>
+        <v>11.5118176569163</v>
       </c>
       <c r="H3" t="n">
         <v>44.8254752081875</v>
@@ -604,13 +604,13 @@
         <v>23</v>
       </c>
       <c r="E4" t="n">
-        <v>-10.4748910736777</v>
+        <v>-9.94075665784715</v>
       </c>
       <c r="F4" t="n">
         <v>-8.55778847280921</v>
       </c>
       <c r="G4" t="n">
-        <v>-10.4748910736777</v>
+        <v>-9.94075665784715</v>
       </c>
       <c r="H4" t="n">
         <v>43.5101752823477</v>
@@ -643,13 +643,13 @@
         <v>23</v>
       </c>
       <c r="E5" t="n">
-        <v>-10.4748910736777</v>
+        <v>-9.94075665784715</v>
       </c>
       <c r="F5" t="n">
         <v>-8.55778847280921</v>
       </c>
       <c r="G5" t="n">
-        <v>-10.4748910736777</v>
+        <v>-9.94075665784715</v>
       </c>
       <c r="H5" t="n">
         <v>43.5101752823477</v>
@@ -682,13 +682,13 @@
         <v>26</v>
       </c>
       <c r="E6" t="n">
-        <v>0.127558722602551</v>
+        <v>-0.522237685546689</v>
       </c>
       <c r="F6" t="n">
         <v>2.04591225597056</v>
       </c>
       <c r="G6" t="n">
-        <v>0.127558722602551</v>
+        <v>-0.522237685546689</v>
       </c>
       <c r="H6" t="n">
         <v>39.0964124200242</v>
@@ -721,13 +721,13 @@
         <v>26</v>
       </c>
       <c r="E7" t="n">
-        <v>0.127558722602551</v>
+        <v>-0.522237685546689</v>
       </c>
       <c r="F7" t="n">
         <v>2.04591225597056</v>
       </c>
       <c r="G7" t="n">
-        <v>0.127558722602551</v>
+        <v>-0.522237685546689</v>
       </c>
       <c r="H7" t="n">
         <v>39.0964124200242</v>

--- a/files/NRLW_upcoming_projections.xlsx
+++ b/files/NRLW_upcoming_projections.xlsx
@@ -53,73 +53,73 @@
     <t xml:space="preserve">Weather Applied</t>
   </si>
   <si>
+    <t xml:space="preserve">12:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain (Primary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No - primary model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted (Reference)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference only - heuristic -0.3 total pts/mm, cap +/-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
     <t xml:space="preserve">15:15</t>
   </si>
   <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wests tigers</t>
+  </si>
+  <si>
     <t xml:space="preserve">canterbury bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain (Primary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No - primary model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted (Reference)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference only - heuristic -0.3 total pts/mm, cap +/-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
   </si>
 </sst>
 </file>
@@ -458,8 +458,8 @@
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="5.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="29.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="24.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="24.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="29.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="26.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="15.71" hidden="0" customWidth="1"/>
@@ -514,7 +514,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
@@ -526,16 +526,16 @@
         <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>11.5118176569163</v>
+        <v>0.970555548632621</v>
       </c>
       <c r="F2" t="n">
-        <v>9.14436818066069</v>
+        <v>0.762667874913196</v>
       </c>
       <c r="G2" t="n">
-        <v>11.5118176569163</v>
+        <v>0.970555548632621</v>
       </c>
       <c r="H2" t="n">
-        <v>44.8254752081875</v>
+        <v>44.7270830947001</v>
       </c>
       <c r="I2" t="s">
         <v>16</v>
@@ -553,7 +553,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -565,16 +565,16 @@
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>11.5118176569163</v>
+        <v>0.970555548632621</v>
       </c>
       <c r="F3" t="n">
-        <v>9.14436818066069</v>
+        <v>0.762667874913196</v>
       </c>
       <c r="G3" t="n">
-        <v>11.5118176569163</v>
+        <v>0.970555548632621</v>
       </c>
       <c r="H3" t="n">
-        <v>44.8254752081875</v>
+        <v>44.7270830947001</v>
       </c>
       <c r="I3" t="s">
         <v>16</v>
@@ -592,7 +592,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
@@ -604,16 +604,16 @@
         <v>23</v>
       </c>
       <c r="E4" t="n">
-        <v>-9.94075665784715</v>
+        <v>11.5103882702689</v>
       </c>
       <c r="F4" t="n">
-        <v>-8.55778847280921</v>
+        <v>8.3362311670229</v>
       </c>
       <c r="G4" t="n">
-        <v>-9.94075665784715</v>
+        <v>11.5103882702689</v>
       </c>
       <c r="H4" t="n">
-        <v>43.5101752823477</v>
+        <v>45.9607130321215</v>
       </c>
       <c r="I4" t="s">
         <v>16</v>
@@ -631,7 +631,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
@@ -643,16 +643,16 @@
         <v>23</v>
       </c>
       <c r="E5" t="n">
-        <v>-9.94075665784715</v>
+        <v>11.5103882702689</v>
       </c>
       <c r="F5" t="n">
-        <v>-8.55778847280921</v>
+        <v>8.3362311670229</v>
       </c>
       <c r="G5" t="n">
-        <v>-9.94075665784715</v>
+        <v>11.5103882702689</v>
       </c>
       <c r="H5" t="n">
-        <v>43.5101752823477</v>
+        <v>45.9607130321215</v>
       </c>
       <c r="I5" t="s">
         <v>16</v>
@@ -670,7 +670,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -682,16 +682,16 @@
         <v>26</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.522237685546689</v>
+        <v>-23.3091190966636</v>
       </c>
       <c r="F6" t="n">
-        <v>2.04591225597056</v>
+        <v>-21.1857518178158</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.522237685546689</v>
+        <v>-23.3091190966636</v>
       </c>
       <c r="H6" t="n">
-        <v>39.0964124200242</v>
+        <v>48.3237177526869</v>
       </c>
       <c r="I6" t="s">
         <v>16</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
@@ -721,16 +721,16 @@
         <v>26</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.522237685546689</v>
+        <v>-23.3091190966636</v>
       </c>
       <c r="F7" t="n">
-        <v>2.04591225597056</v>
+        <v>-21.1857518178158</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.522237685546689</v>
+        <v>-23.3091190966636</v>
       </c>
       <c r="H7" t="n">
-        <v>39.0964124200242</v>
+        <v>48.3237177526869</v>
       </c>
       <c r="I7" t="s">
         <v>16</v>
@@ -748,7 +748,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46257</v>
+        <v>46264</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
@@ -760,16 +760,16 @@
         <v>29</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.72619030904951</v>
+        <v>17.9639971375428</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.50377486850017</v>
+        <v>15.0443716893046</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.72619030904951</v>
+        <v>17.9639971375428</v>
       </c>
       <c r="H8" t="n">
-        <v>41.0357964870386</v>
+        <v>48.655310971524</v>
       </c>
       <c r="I8" t="s">
         <v>16</v>
@@ -787,7 +787,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46257</v>
+        <v>46264</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
@@ -799,16 +799,16 @@
         <v>29</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.72619030904951</v>
+        <v>17.9639971375428</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.50377486850017</v>
+        <v>15.0443716893046</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.72619030904951</v>
+        <v>17.9639971375428</v>
       </c>
       <c r="H9" t="n">
-        <v>41.0357964870386</v>
+        <v>48.655310971524</v>
       </c>
       <c r="I9" t="s">
         <v>16</v>
@@ -826,7 +826,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46257</v>
+        <v>46264</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
@@ -838,16 +838,16 @@
         <v>32</v>
       </c>
       <c r="E10" t="n">
-        <v>10.687527216143</v>
+        <v>-8.75014719643508</v>
       </c>
       <c r="F10" t="n">
-        <v>7.48263222765156</v>
+        <v>-5.82688755199425</v>
       </c>
       <c r="G10" t="n">
-        <v>10.687527216143</v>
+        <v>-8.75014719643508</v>
       </c>
       <c r="H10" t="n">
-        <v>42.8875078910283</v>
+        <v>44.3987244916337</v>
       </c>
       <c r="I10" t="s">
         <v>16</v>
@@ -865,7 +865,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46257</v>
+        <v>46264</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
@@ -877,16 +877,16 @@
         <v>32</v>
       </c>
       <c r="E11" t="n">
-        <v>10.687527216143</v>
+        <v>-8.75014719643508</v>
       </c>
       <c r="F11" t="n">
-        <v>7.48263222765156</v>
+        <v>-5.82688755199425</v>
       </c>
       <c r="G11" t="n">
-        <v>10.687527216143</v>
+        <v>-8.75014719643508</v>
       </c>
       <c r="H11" t="n">
-        <v>42.8875078910283</v>
+        <v>44.3987244916337</v>
       </c>
       <c r="I11" t="s">
         <v>16</v>
@@ -904,7 +904,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46257</v>
+        <v>46264</v>
       </c>
       <c r="B12" t="s">
         <v>33</v>
@@ -916,16 +916,16 @@
         <v>35</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.9684320847818</v>
+        <v>-7.68554636006098</v>
       </c>
       <c r="F12" t="n">
-        <v>-13.1994092539009</v>
+        <v>-4.83302841434709</v>
       </c>
       <c r="G12" t="n">
-        <v>-10.9684320847818</v>
+        <v>-7.68554636006098</v>
       </c>
       <c r="H12" t="n">
-        <v>44.3871229917024</v>
+        <v>50.2409173785568</v>
       </c>
       <c r="I12" t="s">
         <v>16</v>
@@ -943,7 +943,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46257</v>
+        <v>46264</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
@@ -955,16 +955,16 @@
         <v>35</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.9684320847818</v>
+        <v>-7.68554636006098</v>
       </c>
       <c r="F13" t="n">
-        <v>-13.1994092539009</v>
+        <v>-4.83302841434709</v>
       </c>
       <c r="G13" t="n">
-        <v>-10.9684320847818</v>
+        <v>-7.68554636006098</v>
       </c>
       <c r="H13" t="n">
-        <v>44.3871229917024</v>
+        <v>50.2409173785568</v>
       </c>
       <c r="I13" t="s">
         <v>16</v>

--- a/files/NRLW_upcoming_projections.xlsx
+++ b/files/NRLW_upcoming_projections.xlsx
@@ -53,73 +53,73 @@
     <t xml:space="preserve">Weather Applied</t>
   </si>
   <si>
+    <t xml:space="preserve">17:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain (Primary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No - primary model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted (Reference)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference only - heuristic -0.3 total pts/mm, cap +/-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
     <t xml:space="preserve">12:45</t>
   </si>
   <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wests tigers</t>
+  </si>
+  <si>
     <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain (Primary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No - primary model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted (Reference)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference only - heuristic -0.3 total pts/mm, cap +/-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury bankstown bulldogs</t>
   </si>
 </sst>
 </file>
@@ -458,7 +458,7 @@
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="5.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="24.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="27.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="29.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="26.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
@@ -514,7 +514,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46263</v>
+        <v>46270</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
@@ -526,16 +526,16 @@
         <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>0.970555548632621</v>
+        <v>-21.2845658417278</v>
       </c>
       <c r="F2" t="n">
-        <v>0.762667874913196</v>
+        <v>-14.9779785202994</v>
       </c>
       <c r="G2" t="n">
-        <v>0.970555548632621</v>
+        <v>-21.2845658417278</v>
       </c>
       <c r="H2" t="n">
-        <v>44.7270830947001</v>
+        <v>47.2398588571231</v>
       </c>
       <c r="I2" t="s">
         <v>16</v>
@@ -553,7 +553,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46263</v>
+        <v>46270</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -565,16 +565,16 @@
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>0.970555548632621</v>
+        <v>-21.2845658417278</v>
       </c>
       <c r="F3" t="n">
-        <v>0.762667874913196</v>
+        <v>-14.9779785202994</v>
       </c>
       <c r="G3" t="n">
-        <v>0.970555548632621</v>
+        <v>-21.2845658417278</v>
       </c>
       <c r="H3" t="n">
-        <v>44.7270830947001</v>
+        <v>47.2398588571231</v>
       </c>
       <c r="I3" t="s">
         <v>16</v>
@@ -592,7 +592,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46263</v>
+        <v>46270</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
@@ -604,16 +604,16 @@
         <v>23</v>
       </c>
       <c r="E4" t="n">
-        <v>11.5103882702689</v>
+        <v>30.5261300432958</v>
       </c>
       <c r="F4" t="n">
-        <v>8.3362311670229</v>
+        <v>26.3094274881499</v>
       </c>
       <c r="G4" t="n">
-        <v>11.5103882702689</v>
+        <v>30.5261300432958</v>
       </c>
       <c r="H4" t="n">
-        <v>45.9607130321215</v>
+        <v>51.0406389659233</v>
       </c>
       <c r="I4" t="s">
         <v>16</v>
@@ -631,7 +631,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46263</v>
+        <v>46270</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
@@ -643,16 +643,16 @@
         <v>23</v>
       </c>
       <c r="E5" t="n">
-        <v>11.5103882702689</v>
+        <v>30.5261300432958</v>
       </c>
       <c r="F5" t="n">
-        <v>8.3362311670229</v>
+        <v>26.3094274881499</v>
       </c>
       <c r="G5" t="n">
-        <v>11.5103882702689</v>
+        <v>30.5261300432958</v>
       </c>
       <c r="H5" t="n">
-        <v>45.9607130321215</v>
+        <v>51.0406389659233</v>
       </c>
       <c r="I5" t="s">
         <v>16</v>
@@ -670,7 +670,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46263</v>
+        <v>46270</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -682,16 +682,16 @@
         <v>26</v>
       </c>
       <c r="E6" t="n">
-        <v>-23.3091190966636</v>
+        <v>-0.277372229678777</v>
       </c>
       <c r="F6" t="n">
-        <v>-21.1857518178158</v>
+        <v>-2.16782103051249</v>
       </c>
       <c r="G6" t="n">
-        <v>-23.3091190966636</v>
+        <v>-0.277372229678777</v>
       </c>
       <c r="H6" t="n">
-        <v>48.3237177526869</v>
+        <v>45.9626217070528</v>
       </c>
       <c r="I6" t="s">
         <v>16</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46263</v>
+        <v>46270</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
@@ -721,16 +721,16 @@
         <v>26</v>
       </c>
       <c r="E7" t="n">
-        <v>-23.3091190966636</v>
+        <v>-0.277372229678777</v>
       </c>
       <c r="F7" t="n">
-        <v>-21.1857518178158</v>
+        <v>-2.16782103051249</v>
       </c>
       <c r="G7" t="n">
-        <v>-23.3091190966636</v>
+        <v>-0.277372229678777</v>
       </c>
       <c r="H7" t="n">
-        <v>48.3237177526869</v>
+        <v>45.9626217070528</v>
       </c>
       <c r="I7" t="s">
         <v>16</v>
@@ -748,7 +748,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46264</v>
+        <v>46271</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
@@ -760,16 +760,16 @@
         <v>29</v>
       </c>
       <c r="E8" t="n">
-        <v>17.9639971375428</v>
+        <v>-8.49258521636964</v>
       </c>
       <c r="F8" t="n">
-        <v>15.0443716893046</v>
+        <v>-11.0034571303145</v>
       </c>
       <c r="G8" t="n">
-        <v>17.9639971375428</v>
+        <v>-8.49258521636964</v>
       </c>
       <c r="H8" t="n">
-        <v>48.655310971524</v>
+        <v>48.3921495377286</v>
       </c>
       <c r="I8" t="s">
         <v>16</v>
@@ -787,7 +787,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46264</v>
+        <v>46271</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
@@ -799,16 +799,16 @@
         <v>29</v>
       </c>
       <c r="E9" t="n">
-        <v>17.9639971375428</v>
+        <v>-8.49258521636964</v>
       </c>
       <c r="F9" t="n">
-        <v>15.0443716893046</v>
+        <v>-11.0034571303145</v>
       </c>
       <c r="G9" t="n">
-        <v>17.9639971375428</v>
+        <v>-8.49258521636964</v>
       </c>
       <c r="H9" t="n">
-        <v>48.655310971524</v>
+        <v>48.3921495377286</v>
       </c>
       <c r="I9" t="s">
         <v>16</v>
@@ -826,7 +826,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46264</v>
+        <v>46271</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
@@ -838,16 +838,16 @@
         <v>32</v>
       </c>
       <c r="E10" t="n">
-        <v>-8.75014719643508</v>
+        <v>22.9694768983296</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.82688755199425</v>
+        <v>19.8064922335625</v>
       </c>
       <c r="G10" t="n">
-        <v>-8.75014719643508</v>
+        <v>22.9694768983296</v>
       </c>
       <c r="H10" t="n">
-        <v>44.3987244916337</v>
+        <v>45.5780383119163</v>
       </c>
       <c r="I10" t="s">
         <v>16</v>
@@ -865,7 +865,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46264</v>
+        <v>46271</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
@@ -877,16 +877,16 @@
         <v>32</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.75014719643508</v>
+        <v>22.9694768983296</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.82688755199425</v>
+        <v>19.8064922335625</v>
       </c>
       <c r="G11" t="n">
-        <v>-8.75014719643508</v>
+        <v>22.9694768983296</v>
       </c>
       <c r="H11" t="n">
-        <v>44.3987244916337</v>
+        <v>45.5780383119163</v>
       </c>
       <c r="I11" t="s">
         <v>16</v>
@@ -904,7 +904,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46264</v>
+        <v>46271</v>
       </c>
       <c r="B12" t="s">
         <v>33</v>
@@ -916,16 +916,16 @@
         <v>35</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.68554636006098</v>
+        <v>6.62246924926246</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.83302841434709</v>
+        <v>7.85739370148368</v>
       </c>
       <c r="G12" t="n">
-        <v>-7.68554636006098</v>
+        <v>6.62246924926246</v>
       </c>
       <c r="H12" t="n">
-        <v>50.2409173785568</v>
+        <v>48.5993859053061</v>
       </c>
       <c r="I12" t="s">
         <v>16</v>
@@ -943,7 +943,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46264</v>
+        <v>46271</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
@@ -955,16 +955,16 @@
         <v>35</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.68554636006098</v>
+        <v>6.62246924926246</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.83302841434709</v>
+        <v>7.85739370148368</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.68554636006098</v>
+        <v>6.62246924926246</v>
       </c>
       <c r="H13" t="n">
-        <v>50.2409173785568</v>
+        <v>48.5993859053061</v>
       </c>
       <c r="I13" t="s">
         <v>16</v>

--- a/files/NRLW_upcoming_projections.xlsx
+++ b/files/NRLW_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -120,6 +120,12 @@
   </si>
   <si>
     <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:40</t>
   </si>
 </sst>
 </file>
@@ -526,13 +532,13 @@
         <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>-21.2845658417278</v>
+        <v>-10.776179076799</v>
       </c>
       <c r="F2" t="n">
         <v>-14.9779785202994</v>
       </c>
       <c r="G2" t="n">
-        <v>-21.2845658417278</v>
+        <v>-10.776179076799</v>
       </c>
       <c r="H2" t="n">
         <v>47.2398588571231</v>
@@ -565,13 +571,13 @@
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>-21.2845658417278</v>
+        <v>-10.776179076799</v>
       </c>
       <c r="F3" t="n">
         <v>-14.9779785202994</v>
       </c>
       <c r="G3" t="n">
-        <v>-21.2845658417278</v>
+        <v>-10.776179076799</v>
       </c>
       <c r="H3" t="n">
         <v>47.2398588571231</v>
@@ -604,13 +610,13 @@
         <v>23</v>
       </c>
       <c r="E4" t="n">
-        <v>30.5261300432958</v>
+        <v>19.8275373642391</v>
       </c>
       <c r="F4" t="n">
         <v>26.3094274881499</v>
       </c>
       <c r="G4" t="n">
-        <v>30.5261300432958</v>
+        <v>19.8275373642391</v>
       </c>
       <c r="H4" t="n">
         <v>51.0406389659233</v>
@@ -643,13 +649,13 @@
         <v>23</v>
       </c>
       <c r="E5" t="n">
-        <v>30.5261300432958</v>
+        <v>19.8275373642391</v>
       </c>
       <c r="F5" t="n">
         <v>26.3094274881499</v>
       </c>
       <c r="G5" t="n">
-        <v>30.5261300432958</v>
+        <v>19.8275373642391</v>
       </c>
       <c r="H5" t="n">
         <v>51.0406389659233</v>
@@ -682,13 +688,13 @@
         <v>26</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.277372229678777</v>
+        <v>-0.0601096892439512</v>
       </c>
       <c r="F6" t="n">
         <v>-2.16782103051249</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.277372229678777</v>
+        <v>-0.0601096892439512</v>
       </c>
       <c r="H6" t="n">
         <v>45.9626217070528</v>
@@ -721,13 +727,13 @@
         <v>26</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.277372229678777</v>
+        <v>-0.0601096892439512</v>
       </c>
       <c r="F7" t="n">
         <v>-2.16782103051249</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.277372229678777</v>
+        <v>-0.0601096892439512</v>
       </c>
       <c r="H7" t="n">
         <v>45.9626217070528</v>
@@ -760,13 +766,13 @@
         <v>29</v>
       </c>
       <c r="E8" t="n">
-        <v>-8.49258521636964</v>
+        <v>-10.7773699815042</v>
       </c>
       <c r="F8" t="n">
         <v>-11.0034571303145</v>
       </c>
       <c r="G8" t="n">
-        <v>-8.49258521636964</v>
+        <v>-10.7773699815042</v>
       </c>
       <c r="H8" t="n">
         <v>48.3921495377286</v>
@@ -799,13 +805,13 @@
         <v>29</v>
       </c>
       <c r="E9" t="n">
-        <v>-8.49258521636964</v>
+        <v>-10.7773699815042</v>
       </c>
       <c r="F9" t="n">
         <v>-11.0034571303145</v>
       </c>
       <c r="G9" t="n">
-        <v>-8.49258521636964</v>
+        <v>-10.7773699815042</v>
       </c>
       <c r="H9" t="n">
         <v>48.3921495377286</v>
@@ -916,13 +922,13 @@
         <v>35</v>
       </c>
       <c r="E12" t="n">
-        <v>6.62246924926246</v>
+        <v>6.07799441320952</v>
       </c>
       <c r="F12" t="n">
         <v>7.85739370148368</v>
       </c>
       <c r="G12" t="n">
-        <v>6.62246924926246</v>
+        <v>6.07799441320952</v>
       </c>
       <c r="H12" t="n">
         <v>48.5993859053061</v>
@@ -955,13 +961,13 @@
         <v>35</v>
       </c>
       <c r="E13" t="n">
-        <v>6.62246924926246</v>
+        <v>6.07799441320952</v>
       </c>
       <c r="F13" t="n">
         <v>7.85739370148368</v>
       </c>
       <c r="G13" t="n">
-        <v>6.62246924926246</v>
+        <v>6.07799441320952</v>
       </c>
       <c r="H13" t="n">
         <v>48.5993859053061</v>
@@ -977,6 +983,162 @@
         <v>0</v>
       </c>
       <c r="M13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-13.2743200346638</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-29.3397083690331</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-13.2743200346638</v>
+      </c>
+      <c r="H14" t="n">
+        <v>52.2934462761714</v>
+      </c>
+      <c r="I14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" t="s">
+        <v>17</v>
+      </c>
+      <c r="K14"/>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-13.2743200346638</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-29.3397083690331</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-13.2743200346638</v>
+      </c>
+      <c r="H15" t="n">
+        <v>52.2934462761714</v>
+      </c>
+      <c r="I15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" t="s">
+        <v>19</v>
+      </c>
+      <c r="K15"/>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" t="n">
+        <v>7.70341465512977</v>
+      </c>
+      <c r="F16" t="n">
+        <v>7.16558025129903</v>
+      </c>
+      <c r="G16" t="n">
+        <v>7.70341465512977</v>
+      </c>
+      <c r="H16" t="n">
+        <v>49.7689237456457</v>
+      </c>
+      <c r="I16" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" t="s">
+        <v>17</v>
+      </c>
+      <c r="K16"/>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" t="n">
+        <v>7.70341465512977</v>
+      </c>
+      <c r="F17" t="n">
+        <v>7.16558025129903</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7.70341465512977</v>
+      </c>
+      <c r="H17" t="n">
+        <v>49.7689237456457</v>
+      </c>
+      <c r="I17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K17"/>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="s">
         <v>20</v>
       </c>
     </row>

--- a/files/NRLW_upcoming_projections.xlsx
+++ b/files/NRLW_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -53,79 +53,67 @@
     <t xml:space="preserve">Weather Applied</t>
   </si>
   <si>
-    <t xml:space="preserve">17:15</t>
+    <t xml:space="preserve">19:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain (Primary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No - primary model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted (Reference)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference only - heuristic -0.3 total pts/mm, cap +/-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wests tigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
   </si>
   <si>
     <t xml:space="preserve">newcastle knights</t>
   </si>
   <si>
-    <t xml:space="preserve">canterbury bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain (Primary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No - primary model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted (Reference)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference only - heuristic -0.3 total pts/mm, cap +/-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
     <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:40</t>
   </si>
 </sst>
 </file>
@@ -464,7 +452,7 @@
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="5.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="27.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="26.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="29.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="26.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
@@ -520,7 +508,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46270</v>
+        <v>46275</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
@@ -532,16 +520,16 @@
         <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>-10.776179076799</v>
+        <v>-33.0587341790831</v>
       </c>
       <c r="F2" t="n">
-        <v>-14.9779785202994</v>
+        <v>-32.0781818325738</v>
       </c>
       <c r="G2" t="n">
-        <v>-10.776179076799</v>
+        <v>-33.0587341790831</v>
       </c>
       <c r="H2" t="n">
-        <v>47.2398588571231</v>
+        <v>57.7750513145418</v>
       </c>
       <c r="I2" t="s">
         <v>16</v>
@@ -559,7 +547,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46270</v>
+        <v>46275</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -571,16 +559,16 @@
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>-10.776179076799</v>
+        <v>-33.0587341790831</v>
       </c>
       <c r="F3" t="n">
-        <v>-14.9779785202994</v>
+        <v>-32.0781818325738</v>
       </c>
       <c r="G3" t="n">
-        <v>-10.776179076799</v>
+        <v>-33.0587341790831</v>
       </c>
       <c r="H3" t="n">
-        <v>47.2398588571231</v>
+        <v>57.7750513145418</v>
       </c>
       <c r="I3" t="s">
         <v>16</v>
@@ -598,7 +586,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
@@ -610,16 +598,16 @@
         <v>23</v>
       </c>
       <c r="E4" t="n">
-        <v>19.8275373642391</v>
+        <v>6.39783869543327</v>
       </c>
       <c r="F4" t="n">
-        <v>26.3094274881499</v>
+        <v>10.3637561986678</v>
       </c>
       <c r="G4" t="n">
-        <v>19.8275373642391</v>
+        <v>6.39783869543327</v>
       </c>
       <c r="H4" t="n">
-        <v>51.0406389659233</v>
+        <v>51.1992231110232</v>
       </c>
       <c r="I4" t="s">
         <v>16</v>
@@ -637,7 +625,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
@@ -649,16 +637,16 @@
         <v>23</v>
       </c>
       <c r="E5" t="n">
-        <v>19.8275373642391</v>
+        <v>6.39783869543327</v>
       </c>
       <c r="F5" t="n">
-        <v>26.3094274881499</v>
+        <v>10.3637561986678</v>
       </c>
       <c r="G5" t="n">
-        <v>19.8275373642391</v>
+        <v>6.39783869543327</v>
       </c>
       <c r="H5" t="n">
-        <v>51.0406389659233</v>
+        <v>51.1992231110232</v>
       </c>
       <c r="I5" t="s">
         <v>16</v>
@@ -676,7 +664,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -688,16 +676,16 @@
         <v>26</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0601096892439512</v>
+        <v>-8.14102243765321</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.16782103051249</v>
+        <v>-3.7420798264886</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0601096892439512</v>
+        <v>-8.14102243765321</v>
       </c>
       <c r="H6" t="n">
-        <v>45.9626217070528</v>
+        <v>47.3236763460009</v>
       </c>
       <c r="I6" t="s">
         <v>16</v>
@@ -715,7 +703,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
@@ -727,16 +715,16 @@
         <v>26</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0601096892439512</v>
+        <v>-8.14102243765321</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.16782103051249</v>
+        <v>-3.7420798264886</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0601096892439512</v>
+        <v>-8.14102243765321</v>
       </c>
       <c r="H7" t="n">
-        <v>45.9626217070528</v>
+        <v>47.3236763460009</v>
       </c>
       <c r="I7" t="s">
         <v>16</v>
@@ -754,7 +742,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46271</v>
+        <v>46277</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
@@ -766,16 +754,16 @@
         <v>29</v>
       </c>
       <c r="E8" t="n">
-        <v>-10.7773699815042</v>
+        <v>-1.68356743879907</v>
       </c>
       <c r="F8" t="n">
-        <v>-11.0034571303145</v>
+        <v>-3.47805895338312</v>
       </c>
       <c r="G8" t="n">
-        <v>-10.7773699815042</v>
+        <v>-1.68356743879907</v>
       </c>
       <c r="H8" t="n">
-        <v>48.3921495377286</v>
+        <v>51.1601385612607</v>
       </c>
       <c r="I8" t="s">
         <v>16</v>
@@ -793,7 +781,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46271</v>
+        <v>46277</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
@@ -805,16 +793,16 @@
         <v>29</v>
       </c>
       <c r="E9" t="n">
-        <v>-10.7773699815042</v>
+        <v>-1.68356743879907</v>
       </c>
       <c r="F9" t="n">
-        <v>-11.0034571303145</v>
+        <v>-3.47805895338312</v>
       </c>
       <c r="G9" t="n">
-        <v>-10.7773699815042</v>
+        <v>-1.68356743879907</v>
       </c>
       <c r="H9" t="n">
-        <v>48.3921495377286</v>
+        <v>51.1601385612607</v>
       </c>
       <c r="I9" t="s">
         <v>16</v>
@@ -832,28 +820,28 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46271</v>
+        <v>46278</v>
       </c>
       <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
         <v>30</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>31</v>
       </c>
-      <c r="D10" t="s">
-        <v>32</v>
-      </c>
       <c r="E10" t="n">
-        <v>22.9694768983296</v>
+        <v>-15.9892221973887</v>
       </c>
       <c r="F10" t="n">
-        <v>19.8064922335625</v>
+        <v>-15.6775494166285</v>
       </c>
       <c r="G10" t="n">
-        <v>22.9694768983296</v>
+        <v>-15.9892221973887</v>
       </c>
       <c r="H10" t="n">
-        <v>45.5780383119163</v>
+        <v>53.7234972412487</v>
       </c>
       <c r="I10" t="s">
         <v>16</v>
@@ -871,28 +859,28 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46271</v>
+        <v>46278</v>
       </c>
       <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
         <v>30</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>31</v>
       </c>
-      <c r="D11" t="s">
-        <v>32</v>
-      </c>
       <c r="E11" t="n">
-        <v>22.9694768983296</v>
+        <v>-15.9892221973887</v>
       </c>
       <c r="F11" t="n">
-        <v>19.8064922335625</v>
+        <v>-15.6775494166285</v>
       </c>
       <c r="G11" t="n">
-        <v>22.9694768983296</v>
+        <v>-15.9892221973887</v>
       </c>
       <c r="H11" t="n">
-        <v>45.5780383119163</v>
+        <v>53.7234972412487</v>
       </c>
       <c r="I11" t="s">
         <v>16</v>
@@ -910,28 +898,28 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46271</v>
+        <v>46278</v>
       </c>
       <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s">
         <v>33</v>
       </c>
-      <c r="C12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" t="s">
-        <v>35</v>
-      </c>
       <c r="E12" t="n">
-        <v>6.07799441320952</v>
+        <v>-2.90769907178539</v>
       </c>
       <c r="F12" t="n">
-        <v>7.85739370148368</v>
+        <v>4.70954831425042</v>
       </c>
       <c r="G12" t="n">
-        <v>6.07799441320952</v>
+        <v>-2.90769907178539</v>
       </c>
       <c r="H12" t="n">
-        <v>48.5993859053061</v>
+        <v>49.0954989732176</v>
       </c>
       <c r="I12" t="s">
         <v>16</v>
@@ -949,28 +937,28 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46271</v>
+        <v>46278</v>
       </c>
       <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s">
         <v>33</v>
       </c>
-      <c r="C13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" t="s">
-        <v>35</v>
-      </c>
       <c r="E13" t="n">
-        <v>6.07799441320952</v>
+        <v>-2.90769907178539</v>
       </c>
       <c r="F13" t="n">
-        <v>7.85739370148368</v>
+        <v>4.70954831425042</v>
       </c>
       <c r="G13" t="n">
-        <v>6.07799441320952</v>
+        <v>-2.90769907178539</v>
       </c>
       <c r="H13" t="n">
-        <v>48.5993859053061</v>
+        <v>49.0954989732176</v>
       </c>
       <c r="I13" t="s">
         <v>16</v>
@@ -983,162 +971,6 @@
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>46275</v>
-      </c>
-      <c r="B14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-13.2743200346638</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-29.3397083690331</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-13.2743200346638</v>
-      </c>
-      <c r="H14" t="n">
-        <v>52.2934462761714</v>
-      </c>
-      <c r="I14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" t="s">
-        <v>17</v>
-      </c>
-      <c r="K14"/>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>46275</v>
-      </c>
-      <c r="B15" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-13.2743200346638</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-29.3397083690331</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-13.2743200346638</v>
-      </c>
-      <c r="H15" t="n">
-        <v>52.2934462761714</v>
-      </c>
-      <c r="I15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" t="s">
-        <v>19</v>
-      </c>
-      <c r="K15"/>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>46276</v>
-      </c>
-      <c r="B16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" t="n">
-        <v>7.70341465512977</v>
-      </c>
-      <c r="F16" t="n">
-        <v>7.16558025129903</v>
-      </c>
-      <c r="G16" t="n">
-        <v>7.70341465512977</v>
-      </c>
-      <c r="H16" t="n">
-        <v>49.7689237456457</v>
-      </c>
-      <c r="I16" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" t="s">
-        <v>17</v>
-      </c>
-      <c r="K16"/>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>46276</v>
-      </c>
-      <c r="B17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" t="n">
-        <v>7.70341465512977</v>
-      </c>
-      <c r="F17" t="n">
-        <v>7.16558025129903</v>
-      </c>
-      <c r="G17" t="n">
-        <v>7.70341465512977</v>
-      </c>
-      <c r="H17" t="n">
-        <v>49.7689237456457</v>
-      </c>
-      <c r="I17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" t="s">
-        <v>19</v>
-      </c>
-      <c r="K17"/>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="s">
         <v>20</v>
       </c>
     </row>

--- a/files/NRLW_upcoming_projections.xlsx
+++ b/files/NRLW_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -86,28 +86,31 @@
     <t xml:space="preserve">canberra raiders</t>
   </si>
   <si>
+    <t xml:space="preserve">17:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
     <t xml:space="preserve">13:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
   </si>
   <si>
     <t xml:space="preserve">newcastle knights</t>
@@ -520,13 +523,13 @@
         <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>-33.0587341790831</v>
+        <v>-36.5521715067098</v>
       </c>
       <c r="F2" t="n">
         <v>-32.0781818325738</v>
       </c>
       <c r="G2" t="n">
-        <v>-33.0587341790831</v>
+        <v>-36.5521715067098</v>
       </c>
       <c r="H2" t="n">
         <v>57.7750513145418</v>
@@ -559,13 +562,13 @@
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>-33.0587341790831</v>
+        <v>-36.5521715067098</v>
       </c>
       <c r="F3" t="n">
         <v>-32.0781818325738</v>
       </c>
       <c r="G3" t="n">
-        <v>-33.0587341790831</v>
+        <v>-36.5521715067098</v>
       </c>
       <c r="H3" t="n">
         <v>57.7750513145418</v>
@@ -598,13 +601,13 @@
         <v>23</v>
       </c>
       <c r="E4" t="n">
-        <v>6.39783869543327</v>
+        <v>9.18387977782106</v>
       </c>
       <c r="F4" t="n">
         <v>10.3637561986678</v>
       </c>
       <c r="G4" t="n">
-        <v>6.39783869543327</v>
+        <v>9.18387977782106</v>
       </c>
       <c r="H4" t="n">
         <v>51.1992231110232</v>
@@ -637,13 +640,13 @@
         <v>23</v>
       </c>
       <c r="E5" t="n">
-        <v>6.39783869543327</v>
+        <v>9.18387977782106</v>
       </c>
       <c r="F5" t="n">
         <v>10.3637561986678</v>
       </c>
       <c r="G5" t="n">
-        <v>6.39783869543327</v>
+        <v>9.18387977782106</v>
       </c>
       <c r="H5" t="n">
         <v>51.1992231110232</v>
@@ -676,13 +679,13 @@
         <v>26</v>
       </c>
       <c r="E6" t="n">
-        <v>-8.14102243765321</v>
+        <v>-7.16212433245236</v>
       </c>
       <c r="F6" t="n">
         <v>-3.7420798264886</v>
       </c>
       <c r="G6" t="n">
-        <v>-8.14102243765321</v>
+        <v>-7.16212433245236</v>
       </c>
       <c r="H6" t="n">
         <v>47.3236763460009</v>
@@ -715,13 +718,13 @@
         <v>26</v>
       </c>
       <c r="E7" t="n">
-        <v>-8.14102243765321</v>
+        <v>-7.16212433245236</v>
       </c>
       <c r="F7" t="n">
         <v>-3.7420798264886</v>
       </c>
       <c r="G7" t="n">
-        <v>-8.14102243765321</v>
+        <v>-7.16212433245236</v>
       </c>
       <c r="H7" t="n">
         <v>47.3236763460009</v>
@@ -754,13 +757,13 @@
         <v>29</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.68356743879907</v>
+        <v>-4.40976604263829</v>
       </c>
       <c r="F8" t="n">
         <v>-3.47805895338312</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.68356743879907</v>
+        <v>-4.40976604263829</v>
       </c>
       <c r="H8" t="n">
         <v>51.1601385612607</v>
@@ -793,13 +796,13 @@
         <v>29</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.68356743879907</v>
+        <v>-4.40976604263829</v>
       </c>
       <c r="F9" t="n">
         <v>-3.47805895338312</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.68356743879907</v>
+        <v>-4.40976604263829</v>
       </c>
       <c r="H9" t="n">
         <v>51.1601385612607</v>
@@ -832,13 +835,13 @@
         <v>31</v>
       </c>
       <c r="E10" t="n">
-        <v>-15.9892221973887</v>
+        <v>-16.0907688345636</v>
       </c>
       <c r="F10" t="n">
         <v>-15.6775494166285</v>
       </c>
       <c r="G10" t="n">
-        <v>-15.9892221973887</v>
+        <v>-16.0907688345636</v>
       </c>
       <c r="H10" t="n">
         <v>53.7234972412487</v>
@@ -871,13 +874,13 @@
         <v>31</v>
       </c>
       <c r="E11" t="n">
-        <v>-15.9892221973887</v>
+        <v>-16.0907688345636</v>
       </c>
       <c r="F11" t="n">
         <v>-15.6775494166285</v>
       </c>
       <c r="G11" t="n">
-        <v>-15.9892221973887</v>
+        <v>-16.0907688345636</v>
       </c>
       <c r="H11" t="n">
         <v>53.7234972412487</v>
@@ -901,22 +904,22 @@
         <v>46278</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.90769907178539</v>
+        <v>-1.12430166853877</v>
       </c>
       <c r="F12" t="n">
         <v>4.70954831425042</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.90769907178539</v>
+        <v>-1.12430166853877</v>
       </c>
       <c r="H12" t="n">
         <v>49.0954989732176</v>
@@ -940,22 +943,22 @@
         <v>46278</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.90769907178539</v>
+        <v>-1.12430166853877</v>
       </c>
       <c r="F13" t="n">
         <v>4.70954831425042</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.90769907178539</v>
+        <v>-1.12430166853877</v>
       </c>
       <c r="H13" t="n">
         <v>49.0954989732176</v>
